--- a/SALT/LiKNaCl_MTP_mk2.xlsx
+++ b/SALT/LiKNaCl_MTP_mk2.xlsx
@@ -1,21 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DD0C5E-322A-394F-BAB9-DE22CBD5BD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E5553E-0758-AE4E-8EEC-5EB858AF09F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9980" yWindow="3460" windowWidth="27640" windowHeight="16940" xr2:uid="{AD1F0662-E479-F942-9113-E180C0D161B9}"/>
+    <workbookView xWindow="2120" yWindow="2960" windowWidth="29380" windowHeight="18960" activeTab="1" xr2:uid="{AD1F0662-E479-F942-9113-E180C0D161B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="33.33.33" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'33.33.33'!$U$11:$U$14</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'33.33.33'!$V$11:$V$14</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'33.33.33'!$Y$11:$Y$14</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'33.33.33'!$Z$11:$Z$14</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'33.33.33'!$U$11:$U$14</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'33.33.33'!$V$11:$V$14</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'33.33.33'!$W$11:$W$14</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'33.33.33'!$X$11:$X$14</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'33.33.33'!$Y$11:$Y$14</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'33.33.33'!$Z$11:$Z$14</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'33.33.33'!$U$11:$U$14</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'33.33.33'!$V$11:$V$14</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'33.33.33'!$W$11:$W$14</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'33.33.33'!$W$11:$W$14</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'33.33.33'!$X$11:$X$14</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'33.33.33'!$Y$11:$Y$14</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'33.33.33'!$Z$11:$Z$14</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'33.33.33'!$X$11:$X$14</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'33.33.33'!$Y$11:$Y$14</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'33.33.33'!$Z$11:$Z$14</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'33.33.33'!$U$11:$U$14</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'33.33.33'!$V$11:$V$14</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'33.33.33'!$W$11:$W$14</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'33.33.33'!$X$11:$X$14</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,8 +65,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="75">
   <si>
     <t>mass</t>
   </si>
@@ -214,6 +263,57 @@
   <si>
     <t>MTP-DFT</t>
   </si>
+  <si>
+    <t>All data for LiCl-KCl-NaCl</t>
+  </si>
+  <si>
+    <t>33.33.33</t>
+  </si>
+  <si>
+    <t>12_10</t>
+  </si>
+  <si>
+    <t>14_10</t>
+  </si>
+  <si>
+    <t>16_10</t>
+  </si>
+  <si>
+    <t>12_8</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>katom-step/s</t>
+  </si>
+  <si>
+    <t>J/mol-K</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Cp</t>
+  </si>
+  <si>
+    <t>Speed N</t>
+  </si>
+  <si>
+    <t>Visc</t>
+  </si>
+  <si>
+    <t>BMH-NaCl</t>
+  </si>
+  <si>
+    <t>12_6</t>
+  </si>
+  <si>
+    <t>Slowdown</t>
+  </si>
+  <si>
+    <t>max-min</t>
+  </si>
 </sst>
 </file>
 
@@ -251,11 +351,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2876,6 +2977,1190 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$B$11:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$C$11:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.4239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3734999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3229999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2724999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-285B-1649-BC09-22088F787A95}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$B$11:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$D$11:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.4521982984824864</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4072080172825043</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3646263311944169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3253968124454378</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-285B-1649-BC09-22088F787A95}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$B$11:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$E$11:$E$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.4201392391206853</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3815717960818399</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3349550283232501</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2852095195496671</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-285B-1649-BC09-22088F787A95}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$B$11:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$F$11:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.4469897432071506</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3966767449312834</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.351633331649178</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3003403263059448</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-285B-1649-BC09-22088F787A95}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$B$11:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$G$11:$G$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.4218075477230747</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.37530193246221</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3339748868159742</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2865074461928288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-285B-1649-BC09-22088F787A95}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$B$11:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$H$11:$H$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.4380980575271523</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3937335414873917</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3492239066994554</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3083489522164848</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-285B-1649-BC09-22088F787A95}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2106075567"/>
+        <c:axId val="1740115183"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2106075567"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1600"/>
+          <c:min val="1100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1740115183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1740115183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="1.2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2106075567"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$V$11:$V$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.74217781689879514</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.68435402454914762</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.54371702356252105</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46281511924431556</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1E4E-8F42-ABC7-511DF9ECEECF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$W$11:$W$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.77195398536684023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.63210645684103528</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.54084458290065762</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.49396522682389249</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1E4E-8F42-ABC7-511DF9ECEECF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$X$11:$X$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.7551706534642697</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.67726541896316084</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.53686836095163137</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.50648298217179899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1E4E-8F42-ABC7-511DF9ECEECF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$Y$11:$Y$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.77498233040286679</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.60724491766366162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.58232571573653724</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.50545537991542722</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1E4E-8F42-ABC7-511DF9ECEECF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'33.33.33'!$Z$11:$Z$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.82105716035738963</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.6562868340985637</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.55421865699518158</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.49782599388470555</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-1E4E-8F42-ABC7-511DF9ECEECF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="31609824"/>
+        <c:axId val="1740306687"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="31609824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1600"/>
+          <c:min val="1100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1740306687"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1740306687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.30000000000000004"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="31609824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2917,6 +4202,86 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3988,6 +5353,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -4045,6 +6442,83 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8000191B-E451-2DF0-24E5-85F72FB5E580}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACDA3B1F-1C33-3D90-B4CD-B3D40D8C5960}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9037B503-954B-9E20-BBE2-3973C3335A2E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5254,7 +7728,7 @@
         <v>-7262.84</v>
       </c>
       <c r="M27">
-        <f>E27/SUM(I27:J27)</f>
+        <f t="shared" ref="M27:M58" si="1">E27/SUM(I27:J27)</f>
         <v>33.414899999999996</v>
       </c>
       <c r="N27">
@@ -5288,7 +7762,7 @@
         <v>-5473.08</v>
       </c>
       <c r="Y27">
-        <f>Q27/SUM(U27:V27)</f>
+        <f t="shared" ref="Y27:Y58" si="2">Q27/SUM(U27:V27)</f>
         <v>33.501624999999997</v>
       </c>
       <c r="Z27">
@@ -5322,7 +7796,7 @@
         <v>-7316.27</v>
       </c>
       <c r="AK27">
-        <f>AC27/SUM(AG27:AH27)</f>
+        <f t="shared" ref="AK27:AK58" si="3">AC27/SUM(AG27:AH27)</f>
         <v>45.539437500000005</v>
       </c>
     </row>
@@ -5358,7 +7832,7 @@
         <v>-4185.5200000000004</v>
       </c>
       <c r="M28">
-        <f>E28/SUM(I28:J28)</f>
+        <f t="shared" si="1"/>
         <v>33.340850000000003</v>
       </c>
       <c r="N28">
@@ -5392,7 +7866,7 @@
         <v>-5479.04</v>
       </c>
       <c r="Y28">
-        <f>Q28/SUM(U28:V28)</f>
+        <f t="shared" si="2"/>
         <v>33.59975</v>
       </c>
       <c r="Z28">
@@ -5426,7 +7900,7 @@
         <v>-7738.93</v>
       </c>
       <c r="AK28">
-        <f>AC28/SUM(AG28:AH28)</f>
+        <f t="shared" si="3"/>
         <v>43.949125000000002</v>
       </c>
     </row>
@@ -5462,7 +7936,7 @@
         <v>-4960.1499999999996</v>
       </c>
       <c r="M29">
-        <f>E29/SUM(I29:J29)</f>
+        <f t="shared" si="1"/>
         <v>33.467100000000002</v>
       </c>
       <c r="N29">
@@ -5496,7 +7970,7 @@
         <v>-4798.6499999999996</v>
       </c>
       <c r="Y29">
-        <f>Q29/SUM(U29:V29)</f>
+        <f t="shared" si="2"/>
         <v>33.709187499999999</v>
       </c>
       <c r="Z29">
@@ -5530,7 +8004,7 @@
         <v>-6908.41</v>
       </c>
       <c r="AK29">
-        <f>AC29/SUM(AG29:AH29)</f>
+        <f t="shared" si="3"/>
         <v>42.5985625</v>
       </c>
     </row>
@@ -5566,7 +8040,7 @@
         <v>-6015.87</v>
       </c>
       <c r="M30">
-        <f>E30/SUM(I30:J30)</f>
+        <f t="shared" si="1"/>
         <v>33.829250000000002</v>
       </c>
       <c r="N30">
@@ -5600,7 +8074,7 @@
         <v>-5585.54</v>
       </c>
       <c r="Y30">
-        <f>Q30/SUM(U30:V30)</f>
+        <f t="shared" si="2"/>
         <v>33.851812500000001</v>
       </c>
       <c r="Z30">
@@ -5634,7 +8108,7 @@
         <v>-6490.33</v>
       </c>
       <c r="AK30">
-        <f>AC30/SUM(AG30:AH30)</f>
+        <f t="shared" si="3"/>
         <v>41.459062500000002</v>
       </c>
     </row>
@@ -5670,7 +8144,7 @@
         <v>-7001.91</v>
       </c>
       <c r="M31">
-        <f>E31/SUM(I31:J31)</f>
+        <f t="shared" si="1"/>
         <v>34.335300000000004</v>
       </c>
       <c r="N31">
@@ -5704,7 +8178,7 @@
         <v>-4762.17</v>
       </c>
       <c r="Y31">
-        <f>Q31/SUM(U31:V31)</f>
+        <f t="shared" si="2"/>
         <v>33.946562499999999</v>
       </c>
       <c r="Z31">
@@ -5738,7 +8212,7 @@
         <v>-5830.92</v>
       </c>
       <c r="AK31">
-        <f>AC31/SUM(AG31:AH31)</f>
+        <f t="shared" si="3"/>
         <v>40.444875000000003</v>
       </c>
     </row>
@@ -5774,7 +8248,7 @@
         <v>-5852.63</v>
       </c>
       <c r="M32">
-        <f>E32/SUM(I32:J32)</f>
+        <f t="shared" si="1"/>
         <v>34.753950000000003</v>
       </c>
       <c r="N32">
@@ -5808,7 +8282,7 @@
         <v>-5425.44</v>
       </c>
       <c r="Y32">
-        <f>Q32/SUM(U32:V32)</f>
+        <f t="shared" si="2"/>
         <v>34.016187500000001</v>
       </c>
       <c r="Z32">
@@ -5842,7 +8316,7 @@
         <v>-5127.6499999999996</v>
       </c>
       <c r="AK32">
-        <f>AC32/SUM(AG32:AH32)</f>
+        <f t="shared" si="3"/>
         <v>39.634875000000001</v>
       </c>
     </row>
@@ -5878,7 +8352,7 @@
         <v>-6318.48</v>
       </c>
       <c r="M33">
-        <f>E33/SUM(I33:J33)</f>
+        <f t="shared" si="1"/>
         <v>35.062750000000001</v>
       </c>
       <c r="N33">
@@ -5912,7 +8386,7 @@
         <v>-5389.08</v>
       </c>
       <c r="Y33">
-        <f>Q33/SUM(U33:V33)</f>
+        <f t="shared" si="2"/>
         <v>33.982750000000003</v>
       </c>
       <c r="Z33">
@@ -5946,7 +8420,7 @@
         <v>-5398.29</v>
       </c>
       <c r="AK33">
-        <f>AC33/SUM(AG33:AH33)</f>
+        <f t="shared" si="3"/>
         <v>38.9558125</v>
       </c>
     </row>
@@ -5982,7 +8456,7 @@
         <v>-6575.56</v>
       </c>
       <c r="M34">
-        <f>E34/SUM(I34:J34)</f>
+        <f t="shared" si="1"/>
         <v>35.0717</v>
       </c>
       <c r="N34">
@@ -6016,7 +8490,7 @@
         <v>-5601.48</v>
       </c>
       <c r="Y34">
-        <f>Q34/SUM(U34:V34)</f>
+        <f t="shared" si="2"/>
         <v>33.899687499999999</v>
       </c>
       <c r="Z34">
@@ -6050,7 +8524,7 @@
         <v>-6103.22</v>
       </c>
       <c r="AK34">
-        <f>AC34/SUM(AG34:AH34)</f>
+        <f t="shared" si="3"/>
         <v>38.344749999999998</v>
       </c>
     </row>
@@ -6086,7 +8560,7 @@
         <v>-7880.38</v>
       </c>
       <c r="M35">
-        <f>E35/SUM(I35:J35)</f>
+        <f t="shared" si="1"/>
         <v>34.745849999999997</v>
       </c>
       <c r="N35">
@@ -6120,7 +8594,7 @@
         <v>-5462.04</v>
       </c>
       <c r="Y35">
-        <f>Q35/SUM(U35:V35)</f>
+        <f t="shared" si="2"/>
         <v>33.774374999999999</v>
       </c>
       <c r="Z35">
@@ -6154,7 +8628,7 @@
         <v>-5719.22</v>
       </c>
       <c r="AK35">
-        <f>AC35/SUM(AG35:AH35)</f>
+        <f t="shared" si="3"/>
         <v>37.772500000000001</v>
       </c>
     </row>
@@ -6190,7 +8664,7 @@
         <v>-6611.8</v>
       </c>
       <c r="M36">
-        <f>E36/SUM(I36:J36)</f>
+        <f t="shared" si="1"/>
         <v>34.037649999999999</v>
       </c>
       <c r="N36">
@@ -6224,7 +8698,7 @@
         <v>-5907.78</v>
       </c>
       <c r="Y36">
-        <f>Q36/SUM(U36:V36)</f>
+        <f t="shared" si="2"/>
         <v>33.666437500000001</v>
       </c>
       <c r="Z36">
@@ -6258,7 +8732,7 @@
         <v>-7055.37</v>
       </c>
       <c r="AK36">
-        <f>AC36/SUM(AG36:AH36)</f>
+        <f t="shared" si="3"/>
         <v>37.260374999999996</v>
       </c>
     </row>
@@ -6294,7 +8768,7 @@
         <v>-5176.75</v>
       </c>
       <c r="M37">
-        <f>E37/SUM(I37:J37)</f>
+        <f t="shared" si="1"/>
         <v>33.184249999999999</v>
       </c>
       <c r="N37">
@@ -6328,7 +8802,7 @@
         <v>-5618.7</v>
       </c>
       <c r="Y37">
-        <f>Q37/SUM(U37:V37)</f>
+        <f t="shared" si="2"/>
         <v>33.554250000000003</v>
       </c>
       <c r="Z37">
@@ -6362,7 +8836,7 @@
         <v>-6270.24</v>
       </c>
       <c r="AK37">
-        <f>AC37/SUM(AG37:AH37)</f>
+        <f t="shared" si="3"/>
         <v>36.751374999999996</v>
       </c>
     </row>
@@ -6398,7 +8872,7 @@
         <v>-1998.68</v>
       </c>
       <c r="M38">
-        <f>E38/SUM(I38:J38)</f>
+        <f t="shared" si="1"/>
         <v>32.491100000000003</v>
       </c>
       <c r="N38">
@@ -6432,7 +8906,7 @@
         <v>-5430.22</v>
       </c>
       <c r="Y38">
-        <f>Q38/SUM(U38:V38)</f>
+        <f t="shared" si="2"/>
         <v>33.466750000000005</v>
       </c>
       <c r="Z38">
@@ -6466,7 +8940,7 @@
         <v>-6245.36</v>
       </c>
       <c r="AK38">
-        <f>AC38/SUM(AG38:AH38)</f>
+        <f t="shared" si="3"/>
         <v>36.237312500000002</v>
       </c>
     </row>
@@ -6502,7 +8976,7 @@
         <v>-3616.09</v>
       </c>
       <c r="M39">
-        <f>E39/SUM(I39:J39)</f>
+        <f t="shared" si="1"/>
         <v>32.023850000000003</v>
       </c>
       <c r="N39">
@@ -6536,7 +9010,7 @@
         <v>-4881.5600000000004</v>
       </c>
       <c r="Y39">
-        <f>Q39/SUM(U39:V39)</f>
+        <f t="shared" si="2"/>
         <v>33.355812499999999</v>
       </c>
       <c r="Z39">
@@ -6570,7 +9044,7 @@
         <v>-4976.01</v>
       </c>
       <c r="AK39">
-        <f>AC39/SUM(AG39:AH39)</f>
+        <f t="shared" si="3"/>
         <v>35.730249999999998</v>
       </c>
     </row>
@@ -6606,7 +9080,7 @@
         <v>-1922.69</v>
       </c>
       <c r="M40">
-        <f>E40/SUM(I40:J40)</f>
+        <f t="shared" si="1"/>
         <v>31.861450000000001</v>
       </c>
       <c r="N40">
@@ -6640,7 +9114,7 @@
         <v>-5331.64</v>
       </c>
       <c r="Y40">
-        <f>Q40/SUM(U40:V40)</f>
+        <f t="shared" si="2"/>
         <v>33.2541875</v>
       </c>
       <c r="Z40">
@@ -6674,7 +9148,7 @@
         <v>-5536.72</v>
       </c>
       <c r="AK40">
-        <f>AC40/SUM(AG40:AH40)</f>
+        <f t="shared" si="3"/>
         <v>35.3293125</v>
       </c>
     </row>
@@ -6710,7 +9184,7 @@
         <v>-5763.07</v>
       </c>
       <c r="M41">
-        <f>E41/SUM(I41:J41)</f>
+        <f t="shared" si="1"/>
         <v>32.15005</v>
       </c>
       <c r="N41">
@@ -6744,7 +9218,7 @@
         <v>-4504.59</v>
       </c>
       <c r="Y41">
-        <f>Q41/SUM(U41:V41)</f>
+        <f t="shared" si="2"/>
         <v>33.1845</v>
       </c>
       <c r="Z41">
@@ -6778,7 +9252,7 @@
         <v>-6134.28</v>
       </c>
       <c r="AK41">
-        <f>AC41/SUM(AG41:AH41)</f>
+        <f t="shared" si="3"/>
         <v>34.938375000000001</v>
       </c>
     </row>
@@ -6814,7 +9288,7 @@
         <v>-2840.55</v>
       </c>
       <c r="M42">
-        <f>E42/SUM(I42:J42)</f>
+        <f t="shared" si="1"/>
         <v>32.787649999999999</v>
       </c>
       <c r="N42">
@@ -6848,7 +9322,7 @@
         <v>-5895.41</v>
       </c>
       <c r="Y42">
-        <f>Q42/SUM(U42:V42)</f>
+        <f t="shared" si="2"/>
         <v>33.250999999999998</v>
       </c>
       <c r="Z42">
@@ -6882,7 +9356,7 @@
         <v>-6050.4</v>
       </c>
       <c r="AK42">
-        <f>AC42/SUM(AG42:AH42)</f>
+        <f t="shared" si="3"/>
         <v>34.524000000000001</v>
       </c>
     </row>
@@ -6918,7 +9392,7 @@
         <v>-5401.95</v>
       </c>
       <c r="M43">
-        <f>E43/SUM(I43:J43)</f>
+        <f t="shared" si="1"/>
         <v>33.736750000000001</v>
       </c>
       <c r="N43">
@@ -6952,7 +9426,7 @@
         <v>-6065.59</v>
       </c>
       <c r="Y43">
-        <f>Q43/SUM(U43:V43)</f>
+        <f t="shared" si="2"/>
         <v>33.377624999999995</v>
       </c>
       <c r="Z43">
@@ -6986,7 +9460,7 @@
         <v>-5080.43</v>
       </c>
       <c r="AK43">
-        <f>AC43/SUM(AG43:AH43)</f>
+        <f t="shared" si="3"/>
         <v>34.167124999999999</v>
       </c>
     </row>
@@ -7022,7 +9496,7 @@
         <v>-6823.09</v>
       </c>
       <c r="M44">
-        <f>E44/SUM(I44:J44)</f>
+        <f t="shared" si="1"/>
         <v>34.704549999999998</v>
       </c>
       <c r="N44">
@@ -7056,7 +9530,7 @@
         <v>-5194.71</v>
       </c>
       <c r="Y44">
-        <f>Q44/SUM(U44:V44)</f>
+        <f t="shared" si="2"/>
         <v>33.549624999999999</v>
       </c>
       <c r="Z44">
@@ -7090,7 +9564,7 @@
         <v>-6541.73</v>
       </c>
       <c r="AK44">
-        <f>AC44/SUM(AG44:AH44)</f>
+        <f t="shared" si="3"/>
         <v>33.947749999999999</v>
       </c>
     </row>
@@ -7126,7 +9600,7 @@
         <v>-8828.86</v>
       </c>
       <c r="M45">
-        <f>E45/SUM(I45:J45)</f>
+        <f t="shared" si="1"/>
         <v>35.301050000000004</v>
       </c>
       <c r="N45">
@@ -7160,7 +9634,7 @@
         <v>-5728.48</v>
       </c>
       <c r="Y45">
-        <f>Q45/SUM(U45:V45)</f>
+        <f t="shared" si="2"/>
         <v>33.808624999999999</v>
       </c>
       <c r="Z45">
@@ -7194,7 +9668,7 @@
         <v>-4607.83</v>
       </c>
       <c r="AK45">
-        <f>AC45/SUM(AG45:AH45)</f>
+        <f t="shared" si="3"/>
         <v>33.741</v>
       </c>
     </row>
@@ -7230,7 +9704,7 @@
         <v>-6910.09</v>
       </c>
       <c r="M46">
-        <f>E46/SUM(I46:J46)</f>
+        <f t="shared" si="1"/>
         <v>35.338499999999996</v>
       </c>
       <c r="N46">
@@ -7264,7 +9738,7 @@
         <v>-5288.72</v>
       </c>
       <c r="Y46">
-        <f>Q46/SUM(U46:V46)</f>
+        <f t="shared" si="2"/>
         <v>34.079812499999996</v>
       </c>
       <c r="Z46">
@@ -7298,7 +9772,7 @@
         <v>-5578.79</v>
       </c>
       <c r="AK46">
-        <f>AC46/SUM(AG46:AH46)</f>
+        <f t="shared" si="3"/>
         <v>33.593562499999997</v>
       </c>
     </row>
@@ -7334,7 +9808,7 @@
         <v>-3384.15</v>
       </c>
       <c r="M47">
-        <f>E47/SUM(I47:J47)</f>
+        <f t="shared" si="1"/>
         <v>35.12435</v>
       </c>
       <c r="N47">
@@ -7368,7 +9842,7 @@
         <v>-5843.3</v>
       </c>
       <c r="Y47">
-        <f>Q47/SUM(U47:V47)</f>
+        <f t="shared" si="2"/>
         <v>34.314687499999998</v>
       </c>
       <c r="Z47">
@@ -7402,7 +9876,7 @@
         <v>-5061.72</v>
       </c>
       <c r="AK47">
-        <f>AC47/SUM(AG47:AH47)</f>
+        <f t="shared" si="3"/>
         <v>33.469749999999998</v>
       </c>
     </row>
@@ -7438,7 +9912,7 @@
         <v>-5869.88</v>
       </c>
       <c r="M48">
-        <f>E48/SUM(I48:J48)</f>
+        <f t="shared" si="1"/>
         <v>34.844850000000001</v>
       </c>
       <c r="N48">
@@ -7472,7 +9946,7 @@
         <v>-5516.13</v>
       </c>
       <c r="Y48">
-        <f>Q48/SUM(U48:V48)</f>
+        <f t="shared" si="2"/>
         <v>34.436062499999998</v>
       </c>
       <c r="Z48">
@@ -7506,7 +9980,7 @@
         <v>-5954.37</v>
       </c>
       <c r="AK48">
-        <f>AC48/SUM(AG48:AH48)</f>
+        <f t="shared" si="3"/>
         <v>33.381187500000003</v>
       </c>
     </row>
@@ -7542,7 +10016,7 @@
         <v>-6753.96</v>
       </c>
       <c r="M49">
-        <f>E49/SUM(I49:J49)</f>
+        <f t="shared" si="1"/>
         <v>34.4649</v>
       </c>
       <c r="N49">
@@ -7576,7 +10050,7 @@
         <v>-6043.1</v>
       </c>
       <c r="Y49">
-        <f>Q49/SUM(U49:V49)</f>
+        <f t="shared" si="2"/>
         <v>34.444937500000002</v>
       </c>
       <c r="Z49">
@@ -7610,7 +10084,7 @@
         <v>-4308.6000000000004</v>
       </c>
       <c r="AK49">
-        <f>AC49/SUM(AG49:AH49)</f>
+        <f t="shared" si="3"/>
         <v>33.326687499999998</v>
       </c>
     </row>
@@ -7646,7 +10120,7 @@
         <v>-6061.05</v>
       </c>
       <c r="M50">
-        <f>E50/SUM(I50:J50)</f>
+        <f t="shared" si="1"/>
         <v>33.987299999999998</v>
       </c>
       <c r="N50">
@@ -7680,7 +10154,7 @@
         <v>-5899.62</v>
       </c>
       <c r="Y50">
-        <f>Q50/SUM(U50:V50)</f>
+        <f t="shared" si="2"/>
         <v>34.288312500000004</v>
       </c>
       <c r="Z50">
@@ -7714,7 +10188,7 @@
         <v>-4912.92</v>
       </c>
       <c r="AK50">
-        <f>AC50/SUM(AG50:AH50)</f>
+        <f t="shared" si="3"/>
         <v>33.407249999999998</v>
       </c>
     </row>
@@ -7750,7 +10224,7 @@
         <v>-5345.86</v>
       </c>
       <c r="M51">
-        <f>E51/SUM(I51:J51)</f>
+        <f t="shared" si="1"/>
         <v>33.554699999999997</v>
       </c>
       <c r="N51">
@@ -7784,7 +10258,7 @@
         <v>-5732.58</v>
       </c>
       <c r="Y51">
-        <f>Q51/SUM(U51:V51)</f>
+        <f t="shared" si="2"/>
         <v>33.958812500000001</v>
       </c>
       <c r="Z51">
@@ -7818,7 +10292,7 @@
         <v>-5286.21</v>
       </c>
       <c r="AK51">
-        <f>AC51/SUM(AG51:AH51)</f>
+        <f t="shared" si="3"/>
         <v>33.519374999999997</v>
       </c>
     </row>
@@ -7854,7 +10328,7 @@
         <v>-4255.79</v>
       </c>
       <c r="M52">
-        <f>E52/SUM(I52:J52)</f>
+        <f t="shared" si="1"/>
         <v>33.365000000000002</v>
       </c>
       <c r="N52">
@@ -7888,7 +10362,7 @@
         <v>-3849.97</v>
       </c>
       <c r="Y52">
-        <f>Q52/SUM(U52:V52)</f>
+        <f t="shared" si="2"/>
         <v>33.574874999999999</v>
       </c>
       <c r="Z52">
@@ -7922,7 +10396,7 @@
         <v>-5592.82</v>
       </c>
       <c r="AK52">
-        <f>AC52/SUM(AG52:AH52)</f>
+        <f t="shared" si="3"/>
         <v>33.642375000000001</v>
       </c>
     </row>
@@ -7958,7 +10432,7 @@
         <v>-2245.44</v>
       </c>
       <c r="M53">
-        <f>E53/SUM(I53:J53)</f>
+        <f t="shared" si="1"/>
         <v>33.354050000000001</v>
       </c>
       <c r="N53">
@@ -7992,7 +10466,7 @@
         <v>-5900.24</v>
       </c>
       <c r="Y53">
-        <f>Q53/SUM(U53:V53)</f>
+        <f t="shared" si="2"/>
         <v>33.288874999999997</v>
       </c>
       <c r="Z53">
@@ -8026,7 +10500,7 @@
         <v>-4130.5</v>
       </c>
       <c r="AK53">
-        <f>AC53/SUM(AG53:AH53)</f>
+        <f t="shared" si="3"/>
         <v>33.696562499999999</v>
       </c>
     </row>
@@ -8062,7 +10536,7 @@
         <v>-7137.98</v>
       </c>
       <c r="M54">
-        <f>E54/SUM(I54:J54)</f>
+        <f t="shared" si="1"/>
         <v>33.517049999999998</v>
       </c>
       <c r="N54">
@@ -8096,7 +10570,7 @@
         <v>-3859.51</v>
       </c>
       <c r="Y54">
-        <f>Q54/SUM(U54:V54)</f>
+        <f t="shared" si="2"/>
         <v>33.060937500000001</v>
       </c>
       <c r="Z54">
@@ -8130,7 +10604,7 @@
         <v>-6226.23</v>
       </c>
       <c r="AK54">
-        <f>AC54/SUM(AG54:AH54)</f>
+        <f t="shared" si="3"/>
         <v>33.7466875</v>
       </c>
     </row>
@@ -8166,7 +10640,7 @@
         <v>-4326.82</v>
       </c>
       <c r="M55">
-        <f>E55/SUM(I55:J55)</f>
+        <f t="shared" si="1"/>
         <v>33.495149999999995</v>
       </c>
       <c r="N55">
@@ -8200,7 +10674,7 @@
         <v>-5156.8900000000003</v>
       </c>
       <c r="Y55">
-        <f>Q55/SUM(U55:V55)</f>
+        <f t="shared" si="2"/>
         <v>33.014812499999998</v>
       </c>
       <c r="Z55">
@@ -8234,7 +10708,7 @@
         <v>-6364.94</v>
       </c>
       <c r="AK55">
-        <f>AC55/SUM(AG55:AH55)</f>
+        <f t="shared" si="3"/>
         <v>33.777250000000002</v>
       </c>
     </row>
@@ -8270,7 +10744,7 @@
         <v>-4088.09</v>
       </c>
       <c r="M56">
-        <f>E56/SUM(I56:J56)</f>
+        <f t="shared" si="1"/>
         <v>33.467150000000004</v>
       </c>
       <c r="N56">
@@ -8304,7 +10778,7 @@
         <v>-4633.59</v>
       </c>
       <c r="Y56">
-        <f>Q56/SUM(U56:V56)</f>
+        <f t="shared" si="2"/>
         <v>33.086812500000001</v>
       </c>
       <c r="Z56">
@@ -8338,7 +10812,7 @@
         <v>-5361.33</v>
       </c>
       <c r="AK56">
-        <f>AC56/SUM(AG56:AH56)</f>
+        <f t="shared" si="3"/>
         <v>33.761312500000003</v>
       </c>
     </row>
@@ -8374,7 +10848,7 @@
         <v>-6053.12</v>
       </c>
       <c r="M57">
-        <f>E57/SUM(I57:J57)</f>
+        <f t="shared" si="1"/>
         <v>33.6083</v>
       </c>
       <c r="N57">
@@ -8408,7 +10882,7 @@
         <v>-4577.16</v>
       </c>
       <c r="Y57">
-        <f>Q57/SUM(U57:V57)</f>
+        <f t="shared" si="2"/>
         <v>33.299187499999995</v>
       </c>
       <c r="Z57">
@@ -8442,7 +10916,7 @@
         <v>-5200.25</v>
       </c>
       <c r="AK57">
-        <f>AC57/SUM(AG57:AH57)</f>
+        <f t="shared" si="3"/>
         <v>33.734250000000003</v>
       </c>
     </row>
@@ -8478,7 +10952,7 @@
         <v>-5657.81</v>
       </c>
       <c r="M58">
-        <f>E58/SUM(I58:J58)</f>
+        <f t="shared" si="1"/>
         <v>33.821249999999999</v>
       </c>
       <c r="N58">
@@ -8512,7 +10986,7 @@
         <v>-5233.49</v>
       </c>
       <c r="Y58">
-        <f>Q58/SUM(U58:V58)</f>
+        <f t="shared" si="2"/>
         <v>33.582687499999999</v>
       </c>
       <c r="Z58">
@@ -8546,7 +11020,7 @@
         <v>-5616.54</v>
       </c>
       <c r="AK58">
-        <f>AC58/SUM(AG58:AH58)</f>
+        <f t="shared" si="3"/>
         <v>33.695687499999998</v>
       </c>
     </row>
@@ -8582,7 +11056,7 @@
         <v>-5096.8</v>
       </c>
       <c r="M59">
-        <f>E59/SUM(I59:J59)</f>
+        <f t="shared" ref="M59:M90" si="4">E59/SUM(I59:J59)</f>
         <v>34.008800000000001</v>
       </c>
       <c r="N59">
@@ -8616,7 +11090,7 @@
         <v>-5090.18</v>
       </c>
       <c r="Y59">
-        <f>Q59/SUM(U59:V59)</f>
+        <f t="shared" ref="Y59:Y90" si="5">Q59/SUM(U59:V59)</f>
         <v>33.893124999999998</v>
       </c>
       <c r="Z59">
@@ -8650,7 +11124,7 @@
         <v>-4834.25</v>
       </c>
       <c r="AK59">
-        <f>AC59/SUM(AG59:AH59)</f>
+        <f t="shared" ref="AK59:AK90" si="6">AC59/SUM(AG59:AH59)</f>
         <v>33.645687500000001</v>
       </c>
     </row>
@@ -8686,7 +11160,7 @@
         <v>-4341.01</v>
       </c>
       <c r="M60">
-        <f>E60/SUM(I60:J60)</f>
+        <f t="shared" si="4"/>
         <v>34.331649999999996</v>
       </c>
       <c r="N60">
@@ -8720,7 +11194,7 @@
         <v>-5485.47</v>
       </c>
       <c r="Y60">
-        <f>Q60/SUM(U60:V60)</f>
+        <f t="shared" si="5"/>
         <v>34.096812499999999</v>
       </c>
       <c r="Z60">
@@ -8754,7 +11228,7 @@
         <v>-5533.05</v>
       </c>
       <c r="AK60">
-        <f>AC60/SUM(AG60:AH60)</f>
+        <f t="shared" si="6"/>
         <v>33.632375000000003</v>
       </c>
     </row>
@@ -8790,7 +11264,7 @@
         <v>-5093.21</v>
       </c>
       <c r="M61">
-        <f>E61/SUM(I61:J61)</f>
+        <f t="shared" si="4"/>
         <v>34.652900000000002</v>
       </c>
       <c r="N61">
@@ -8824,7 +11298,7 @@
         <v>-5899.57</v>
       </c>
       <c r="Y61">
-        <f>Q61/SUM(U61:V61)</f>
+        <f t="shared" si="5"/>
         <v>34.154499999999999</v>
       </c>
       <c r="Z61">
@@ -8858,7 +11332,7 @@
         <v>-5330.83</v>
       </c>
       <c r="AK61">
-        <f>AC61/SUM(AG61:AH61)</f>
+        <f t="shared" si="6"/>
         <v>33.614125000000001</v>
       </c>
     </row>
@@ -8894,7 +11368,7 @@
         <v>-6930.95</v>
       </c>
       <c r="M62">
-        <f>E62/SUM(I62:J62)</f>
+        <f t="shared" si="4"/>
         <v>34.821350000000002</v>
       </c>
       <c r="N62">
@@ -8928,7 +11402,7 @@
         <v>-5128.72</v>
       </c>
       <c r="Y62">
-        <f>Q62/SUM(U62:V62)</f>
+        <f t="shared" si="5"/>
         <v>34.097312500000001</v>
       </c>
       <c r="Z62">
@@ -8962,7 +11436,7 @@
         <v>-5791.6</v>
       </c>
       <c r="AK62">
-        <f>AC62/SUM(AG62:AH62)</f>
+        <f t="shared" si="6"/>
         <v>33.617062500000003</v>
       </c>
     </row>
@@ -8998,7 +11472,7 @@
         <v>-8151.61</v>
       </c>
       <c r="M63">
-        <f>E63/SUM(I63:J63)</f>
+        <f t="shared" si="4"/>
         <v>34.887050000000002</v>
       </c>
       <c r="N63">
@@ -9032,7 +11506,7 @@
         <v>-5610.37</v>
       </c>
       <c r="Y63">
-        <f>Q63/SUM(U63:V63)</f>
+        <f t="shared" si="5"/>
         <v>33.976624999999999</v>
       </c>
       <c r="Z63">
@@ -9066,7 +11540,7 @@
         <v>-4510.83</v>
       </c>
       <c r="AK63">
-        <f>AC63/SUM(AG63:AH63)</f>
+        <f t="shared" si="6"/>
         <v>33.625937499999999</v>
       </c>
     </row>
@@ -9102,7 +11576,7 @@
         <v>-6554.94</v>
       </c>
       <c r="M64">
-        <f>E64/SUM(I64:J64)</f>
+        <f t="shared" si="4"/>
         <v>34.617249999999999</v>
       </c>
       <c r="N64">
@@ -9136,7 +11610,7 @@
         <v>-6011.79</v>
       </c>
       <c r="Y64">
-        <f>Q64/SUM(U64:V64)</f>
+        <f t="shared" si="5"/>
         <v>33.826625</v>
       </c>
       <c r="Z64">
@@ -9170,7 +11644,7 @@
         <v>-5289.64</v>
       </c>
       <c r="AK64">
-        <f>AC64/SUM(AG64:AH64)</f>
+        <f t="shared" si="6"/>
         <v>33.660187499999999</v>
       </c>
     </row>
@@ -9206,7 +11680,7 @@
         <v>-3744.03</v>
       </c>
       <c r="M65">
-        <f>E65/SUM(I65:J65)</f>
+        <f t="shared" si="4"/>
         <v>34.208400000000005</v>
       </c>
       <c r="N65">
@@ -9240,7 +11714,7 @@
         <v>-5226.55</v>
       </c>
       <c r="Y65">
-        <f>Q65/SUM(U65:V65)</f>
+        <f t="shared" si="5"/>
         <v>33.697937499999995</v>
       </c>
       <c r="Z65">
@@ -9274,7 +11748,7 @@
         <v>-5745.81</v>
       </c>
       <c r="AK65">
-        <f>AC65/SUM(AG65:AH65)</f>
+        <f t="shared" si="6"/>
         <v>33.660312500000003</v>
       </c>
     </row>
@@ -9310,7 +11784,7 @@
         <v>-3330.99</v>
       </c>
       <c r="M66">
-        <f>E66/SUM(I66:J66)</f>
+        <f t="shared" si="4"/>
         <v>33.82985</v>
       </c>
       <c r="N66">
@@ -9344,7 +11818,7 @@
         <v>-4594.53</v>
       </c>
       <c r="Y66">
-        <f>Q66/SUM(U66:V66)</f>
+        <f t="shared" si="5"/>
         <v>33.59975</v>
       </c>
       <c r="Z66">
@@ -9378,7 +11852,7 @@
         <v>-6011.42</v>
       </c>
       <c r="AK66">
-        <f>AC66/SUM(AG66:AH66)</f>
+        <f t="shared" si="6"/>
         <v>33.646125000000005</v>
       </c>
     </row>
@@ -9414,7 +11888,7 @@
         <v>-5909.5</v>
       </c>
       <c r="M67">
-        <f>E67/SUM(I67:J67)</f>
+        <f t="shared" si="4"/>
         <v>33.515749999999997</v>
       </c>
       <c r="N67">
@@ -9448,7 +11922,7 @@
         <v>-6110.67</v>
       </c>
       <c r="Y67">
-        <f>Q67/SUM(U67:V67)</f>
+        <f t="shared" si="5"/>
         <v>33.505875000000003</v>
       </c>
       <c r="Z67">
@@ -9482,7 +11956,7 @@
         <v>-5377.44</v>
       </c>
       <c r="AK67">
-        <f>AC67/SUM(AG67:AH67)</f>
+        <f t="shared" si="6"/>
         <v>33.588749999999997</v>
       </c>
     </row>
@@ -9518,7 +11992,7 @@
         <v>-4677.87</v>
       </c>
       <c r="M68">
-        <f>E68/SUM(I68:J68)</f>
+        <f t="shared" si="4"/>
         <v>33.244149999999998</v>
       </c>
       <c r="N68">
@@ -9552,7 +12026,7 @@
         <v>-4837.3</v>
       </c>
       <c r="Y68">
-        <f>Q68/SUM(U68:V68)</f>
+        <f t="shared" si="5"/>
         <v>33.426812500000004</v>
       </c>
       <c r="Z68">
@@ -9586,7 +12060,7 @@
         <v>-5581.77</v>
       </c>
       <c r="AK68">
-        <f>AC68/SUM(AG68:AH68)</f>
+        <f t="shared" si="6"/>
         <v>33.549687499999997</v>
       </c>
     </row>
@@ -9622,7 +12096,7 @@
         <v>-6790.99</v>
       </c>
       <c r="M69">
-        <f>E69/SUM(I69:J69)</f>
+        <f t="shared" si="4"/>
         <v>33.139899999999997</v>
       </c>
       <c r="N69">
@@ -9656,7 +12130,7 @@
         <v>-4773.13</v>
       </c>
       <c r="Y69">
-        <f>Q69/SUM(U69:V69)</f>
+        <f t="shared" si="5"/>
         <v>33.401249999999997</v>
       </c>
       <c r="Z69">
@@ -9690,7 +12164,7 @@
         <v>-5560.65</v>
       </c>
       <c r="AK69">
-        <f>AC69/SUM(AG69:AH69)</f>
+        <f t="shared" si="6"/>
         <v>33.527625</v>
       </c>
     </row>
@@ -9726,7 +12200,7 @@
         <v>-4879.17</v>
       </c>
       <c r="M70">
-        <f>E70/SUM(I70:J70)</f>
+        <f t="shared" si="4"/>
         <v>33.1004</v>
       </c>
       <c r="N70">
@@ -9760,7 +12234,7 @@
         <v>-5168.26</v>
       </c>
       <c r="Y70">
-        <f>Q70/SUM(U70:V70)</f>
+        <f t="shared" si="5"/>
         <v>33.435625000000002</v>
       </c>
       <c r="Z70">
@@ -9794,7 +12268,7 @@
         <v>-5761.62</v>
       </c>
       <c r="AK70">
-        <f>AC70/SUM(AG70:AH70)</f>
+        <f t="shared" si="6"/>
         <v>33.526812499999998</v>
       </c>
     </row>
@@ -9830,7 +12304,7 @@
         <v>-4688.3100000000004</v>
       </c>
       <c r="M71">
-        <f>E71/SUM(I71:J71)</f>
+        <f t="shared" si="4"/>
         <v>33.094899999999996</v>
       </c>
       <c r="N71">
@@ -9864,7 +12338,7 @@
         <v>-5572.75</v>
       </c>
       <c r="Y71">
-        <f>Q71/SUM(U71:V71)</f>
+        <f t="shared" si="5"/>
         <v>33.513062500000004</v>
       </c>
       <c r="Z71">
@@ -9898,7 +12372,7 @@
         <v>-5475.46</v>
       </c>
       <c r="AK71">
-        <f>AC71/SUM(AG71:AH71)</f>
+        <f t="shared" si="6"/>
         <v>33.518499999999996</v>
       </c>
     </row>
@@ -9934,7 +12408,7 @@
         <v>-3894.54</v>
       </c>
       <c r="M72">
-        <f>E72/SUM(I72:J72)</f>
+        <f t="shared" si="4"/>
         <v>33.213049999999996</v>
       </c>
       <c r="N72">
@@ -9968,7 +12442,7 @@
         <v>-5958.39</v>
       </c>
       <c r="Y72">
-        <f>Q72/SUM(U72:V72)</f>
+        <f t="shared" si="5"/>
         <v>33.614062500000003</v>
       </c>
       <c r="Z72">
@@ -10002,7 +12476,7 @@
         <v>-3923.93</v>
       </c>
       <c r="AK72">
-        <f>AC72/SUM(AG72:AH72)</f>
+        <f t="shared" si="6"/>
         <v>33.538562499999998</v>
       </c>
     </row>
@@ -10038,7 +12512,7 @@
         <v>-5740.54</v>
       </c>
       <c r="M73">
-        <f>E73/SUM(I73:J73)</f>
+        <f t="shared" si="4"/>
         <v>33.353200000000001</v>
       </c>
       <c r="N73">
@@ -10072,7 +12546,7 @@
         <v>-4979.8500000000004</v>
       </c>
       <c r="Y73">
-        <f>Q73/SUM(U73:V73)</f>
+        <f t="shared" si="5"/>
         <v>33.729937499999998</v>
       </c>
       <c r="Z73">
@@ -10106,7 +12580,7 @@
         <v>-5539.35</v>
       </c>
       <c r="AK73">
-        <f>AC73/SUM(AG73:AH73)</f>
+        <f t="shared" si="6"/>
         <v>33.659999999999997</v>
       </c>
     </row>
@@ -10142,7 +12616,7 @@
         <v>-7640.68</v>
       </c>
       <c r="M74">
-        <f>E74/SUM(I74:J74)</f>
+        <f t="shared" si="4"/>
         <v>33.52975</v>
       </c>
       <c r="N74">
@@ -10176,7 +12650,7 @@
         <v>-5541.88</v>
       </c>
       <c r="Y74">
-        <f>Q74/SUM(U74:V74)</f>
+        <f t="shared" si="5"/>
         <v>33.857750000000003</v>
       </c>
       <c r="Z74">
@@ -10210,7 +12684,7 @@
         <v>-5824.11</v>
       </c>
       <c r="AK74">
-        <f>AC74/SUM(AG74:AH74)</f>
+        <f t="shared" si="6"/>
         <v>33.744749999999996</v>
       </c>
     </row>
@@ -10246,7 +12720,7 @@
         <v>-5149.8</v>
       </c>
       <c r="M75">
-        <f>E75/SUM(I75:J75)</f>
+        <f t="shared" si="4"/>
         <v>33.747050000000002</v>
       </c>
       <c r="N75">
@@ -10280,7 +12754,7 @@
         <v>-5901.06</v>
       </c>
       <c r="Y75">
-        <f>Q75/SUM(U75:V75)</f>
+        <f t="shared" si="5"/>
         <v>33.916874999999997</v>
       </c>
       <c r="Z75">
@@ -10314,7 +12788,7 @@
         <v>-5522.98</v>
       </c>
       <c r="AK75">
-        <f>AC75/SUM(AG75:AH75)</f>
+        <f t="shared" si="6"/>
         <v>33.793812500000001</v>
       </c>
     </row>
@@ -10350,7 +12824,7 @@
         <v>-6799.96</v>
       </c>
       <c r="M76">
-        <f>E76/SUM(I76:J76)</f>
+        <f t="shared" si="4"/>
         <v>33.951999999999998</v>
       </c>
       <c r="N76">
@@ -10384,7 +12858,7 @@
         <v>-5883.21</v>
       </c>
       <c r="Y76">
-        <f>Q76/SUM(U76:V76)</f>
+        <f t="shared" si="5"/>
         <v>33.918187500000002</v>
       </c>
       <c r="Z76">
@@ -10418,7 +12892,7 @@
         <v>-4948.4399999999996</v>
       </c>
       <c r="AK76">
-        <f>AC76/SUM(AG76:AH76)</f>
+        <f t="shared" si="6"/>
         <v>33.855874999999997</v>
       </c>
     </row>
@@ -10454,7 +12928,7 @@
         <v>-7263.74</v>
       </c>
       <c r="M77">
-        <f>E77/SUM(I77:J77)</f>
+        <f t="shared" si="4"/>
         <v>34.036550000000005</v>
       </c>
       <c r="N77">
@@ -10488,7 +12962,7 @@
         <v>-5784.45</v>
       </c>
       <c r="Y77">
-        <f>Q77/SUM(U77:V77)</f>
+        <f t="shared" si="5"/>
         <v>33.897187500000001</v>
       </c>
       <c r="Z77">
@@ -10522,7 +12996,7 @@
         <v>-5355.49</v>
       </c>
       <c r="AK77">
-        <f>AC77/SUM(AG77:AH77)</f>
+        <f t="shared" si="6"/>
         <v>33.9371875</v>
       </c>
     </row>
@@ -10558,7 +13032,7 @@
         <v>-5899.75</v>
       </c>
       <c r="M78">
-        <f>E78/SUM(I78:J78)</f>
+        <f t="shared" si="4"/>
         <v>34.064</v>
       </c>
       <c r="N78">
@@ -10592,7 +13066,7 @@
         <v>-6122.39</v>
       </c>
       <c r="Y78">
-        <f>Q78/SUM(U78:V78)</f>
+        <f t="shared" si="5"/>
         <v>33.805437499999996</v>
       </c>
       <c r="Z78">
@@ -10626,7 +13100,7 @@
         <v>-5552.14</v>
       </c>
       <c r="AK78">
-        <f>AC78/SUM(AG78:AH78)</f>
+        <f t="shared" si="6"/>
         <v>33.983562499999998</v>
       </c>
     </row>
@@ -10662,7 +13136,7 @@
         <v>-4172.55</v>
       </c>
       <c r="M79">
-        <f>E79/SUM(I79:J79)</f>
+        <f t="shared" si="4"/>
         <v>33.94</v>
       </c>
       <c r="N79">
@@ -10696,7 +13170,7 @@
         <v>-4758.5200000000004</v>
       </c>
       <c r="Y79">
-        <f>Q79/SUM(U79:V79)</f>
+        <f t="shared" si="5"/>
         <v>33.6499375</v>
       </c>
       <c r="Z79">
@@ -10730,7 +13204,7 @@
         <v>-6161.64</v>
       </c>
       <c r="AK79">
-        <f>AC79/SUM(AG79:AH79)</f>
+        <f t="shared" si="6"/>
         <v>33.994499999999995</v>
       </c>
     </row>
@@ -10766,7 +13240,7 @@
         <v>-3660.21</v>
       </c>
       <c r="M80">
-        <f>E80/SUM(I80:J80)</f>
+        <f t="shared" si="4"/>
         <v>33.712249999999997</v>
       </c>
       <c r="N80">
@@ -10800,7 +13274,7 @@
         <v>-5889.16</v>
       </c>
       <c r="Y80">
-        <f>Q80/SUM(U80:V80)</f>
+        <f t="shared" si="5"/>
         <v>33.5078125</v>
       </c>
       <c r="Z80">
@@ -10834,7 +13308,7 @@
         <v>-5151.2299999999996</v>
       </c>
       <c r="AK80">
-        <f>AC80/SUM(AG80:AH80)</f>
+        <f t="shared" si="6"/>
         <v>33.917437499999998</v>
       </c>
     </row>
@@ -10870,7 +13344,7 @@
         <v>-6375.55</v>
       </c>
       <c r="M81">
-        <f>E81/SUM(I81:J81)</f>
+        <f t="shared" si="4"/>
         <v>33.506750000000004</v>
       </c>
       <c r="N81">
@@ -10904,7 +13378,7 @@
         <v>-5523.07</v>
       </c>
       <c r="Y81">
-        <f>Q81/SUM(U81:V81)</f>
+        <f t="shared" si="5"/>
         <v>33.379062500000003</v>
       </c>
       <c r="Z81">
@@ -10938,7 +13412,7 @@
         <v>-5783.52</v>
       </c>
       <c r="AK81">
-        <f>AC81/SUM(AG81:AH81)</f>
+        <f t="shared" si="6"/>
         <v>33.811125000000004</v>
       </c>
     </row>
@@ -10974,7 +13448,7 @@
         <v>-6910.3</v>
       </c>
       <c r="M82">
-        <f>E82/SUM(I82:J82)</f>
+        <f t="shared" si="4"/>
         <v>33.1205</v>
       </c>
       <c r="N82">
@@ -11008,7 +13482,7 @@
         <v>-4070.85</v>
       </c>
       <c r="Y82">
-        <f>Q82/SUM(U82:V82)</f>
+        <f t="shared" si="5"/>
         <v>33.274124999999998</v>
       </c>
       <c r="Z82">
@@ -11042,7 +13516,7 @@
         <v>-4834.53</v>
       </c>
       <c r="AK82">
-        <f>AC82/SUM(AG82:AH82)</f>
+        <f t="shared" si="6"/>
         <v>33.657062500000002</v>
       </c>
     </row>
@@ -11078,7 +13552,7 @@
         <v>-2959.53</v>
       </c>
       <c r="M83">
-        <f>E83/SUM(I83:J83)</f>
+        <f t="shared" si="4"/>
         <v>32.572949999999999</v>
       </c>
       <c r="N83">
@@ -11112,7 +13586,7 @@
         <v>-5398.05</v>
       </c>
       <c r="Y83">
-        <f>Q83/SUM(U83:V83)</f>
+        <f t="shared" si="5"/>
         <v>33.260999999999996</v>
       </c>
       <c r="Z83">
@@ -11146,7 +13620,7 @@
         <v>-4928.01</v>
       </c>
       <c r="AK83">
-        <f>AC83/SUM(AG83:AH83)</f>
+        <f t="shared" si="6"/>
         <v>33.524187499999996</v>
       </c>
     </row>
@@ -11182,7 +13656,7 @@
         <v>-3289.35</v>
       </c>
       <c r="M84">
-        <f>E84/SUM(I84:J84)</f>
+        <f t="shared" si="4"/>
         <v>32.214199999999998</v>
       </c>
       <c r="N84">
@@ -11216,7 +13690,7 @@
         <v>-6017.8</v>
       </c>
       <c r="Y84">
-        <f>Q84/SUM(U84:V84)</f>
+        <f t="shared" si="5"/>
         <v>33.333437500000002</v>
       </c>
       <c r="Z84">
@@ -11250,7 +13724,7 @@
         <v>-5564.82</v>
       </c>
       <c r="AK84">
-        <f>AC84/SUM(AG84:AH84)</f>
+        <f t="shared" si="6"/>
         <v>33.434249999999999</v>
       </c>
     </row>
@@ -11286,7 +13760,7 @@
         <v>-4224</v>
       </c>
       <c r="M85">
-        <f>E85/SUM(I85:J85)</f>
+        <f t="shared" si="4"/>
         <v>32.146350000000005</v>
       </c>
       <c r="N85">
@@ -11320,7 +13794,7 @@
         <v>-5084.91</v>
       </c>
       <c r="Y85">
-        <f>Q85/SUM(U85:V85)</f>
+        <f t="shared" si="5"/>
         <v>33.411687499999999</v>
       </c>
       <c r="Z85">
@@ -11354,7 +13828,7 @@
         <v>-4739.4399999999996</v>
       </c>
       <c r="AK85">
-        <f>AC85/SUM(AG85:AH85)</f>
+        <f t="shared" si="6"/>
         <v>33.35275</v>
       </c>
     </row>
@@ -11390,7 +13864,7 @@
         <v>-2683.34</v>
       </c>
       <c r="M86">
-        <f>E86/SUM(I86:J86)</f>
+        <f t="shared" si="4"/>
         <v>32.427100000000003</v>
       </c>
       <c r="N86">
@@ -11424,7 +13898,7 @@
         <v>-4220.8500000000004</v>
       </c>
       <c r="Y86">
-        <f>Q86/SUM(U86:V86)</f>
+        <f t="shared" si="5"/>
         <v>33.507624999999997</v>
       </c>
       <c r="Z86">
@@ -11458,7 +13932,7 @@
         <v>-5020.1899999999996</v>
       </c>
       <c r="AK86">
-        <f>AC86/SUM(AG86:AH86)</f>
+        <f t="shared" si="6"/>
         <v>33.339624999999998</v>
       </c>
     </row>
@@ -11494,7 +13968,7 @@
         <v>-3732.84</v>
       </c>
       <c r="M87">
-        <f>E87/SUM(I87:J87)</f>
+        <f t="shared" si="4"/>
         <v>33.028800000000004</v>
       </c>
       <c r="N87">
@@ -11528,7 +14002,7 @@
         <v>-4832.28</v>
       </c>
       <c r="Y87">
-        <f>Q87/SUM(U87:V87)</f>
+        <f t="shared" si="5"/>
         <v>33.670875000000002</v>
       </c>
       <c r="Z87">
@@ -11562,7 +14036,7 @@
         <v>-5057.29</v>
       </c>
       <c r="AK87">
-        <f>AC87/SUM(AG87:AH87)</f>
+        <f t="shared" si="6"/>
         <v>33.368249999999996</v>
       </c>
     </row>
@@ -11598,7 +14072,7 @@
         <v>-1396.36</v>
       </c>
       <c r="M88">
-        <f>E88/SUM(I88:J88)</f>
+        <f t="shared" si="4"/>
         <v>33.822249999999997</v>
       </c>
       <c r="N88">
@@ -11632,7 +14106,7 @@
         <v>-5180.99</v>
       </c>
       <c r="Y88">
-        <f>Q88/SUM(U88:V88)</f>
+        <f t="shared" si="5"/>
         <v>33.871875000000003</v>
       </c>
       <c r="Z88">
@@ -11666,7 +14140,7 @@
         <v>-4067.34</v>
       </c>
       <c r="AK88">
-        <f>AC88/SUM(AG88:AH88)</f>
+        <f t="shared" si="6"/>
         <v>33.408874999999995</v>
       </c>
     </row>
@@ -11702,7 +14176,7 @@
         <v>-6787.63</v>
       </c>
       <c r="M89">
-        <f>E89/SUM(I89:J89)</f>
+        <f t="shared" si="4"/>
         <v>34.788850000000004</v>
       </c>
       <c r="N89">
@@ -11736,7 +14210,7 @@
         <v>-5779.66</v>
       </c>
       <c r="Y89">
-        <f>Q89/SUM(U89:V89)</f>
+        <f t="shared" si="5"/>
         <v>34.038000000000004</v>
       </c>
       <c r="Z89">
@@ -11770,7 +14244,7 @@
         <v>-5009.71</v>
       </c>
       <c r="AK89">
-        <f>AC89/SUM(AG89:AH89)</f>
+        <f t="shared" si="6"/>
         <v>33.553625000000004</v>
       </c>
     </row>
@@ -11806,7 +14280,7 @@
         <v>-7093.51</v>
       </c>
       <c r="M90">
-        <f>E90/SUM(I90:J90)</f>
+        <f t="shared" si="4"/>
         <v>35.52205</v>
       </c>
       <c r="N90">
@@ -11840,7 +14314,7 @@
         <v>-6890.31</v>
       </c>
       <c r="Y90">
-        <f>Q90/SUM(U90:V90)</f>
+        <f t="shared" si="5"/>
         <v>34.150812500000001</v>
       </c>
       <c r="Z90">
@@ -11874,7 +14348,7 @@
         <v>-4960.04</v>
       </c>
       <c r="AK90">
-        <f>AC90/SUM(AG90:AH90)</f>
+        <f t="shared" si="6"/>
         <v>33.705874999999999</v>
       </c>
     </row>
@@ -11910,7 +14384,7 @@
         <v>-7062.24</v>
       </c>
       <c r="M91">
-        <f>E91/SUM(I91:J91)</f>
+        <f t="shared" ref="M91:M126" si="7">E91/SUM(I91:J91)</f>
         <v>35.874299999999998</v>
       </c>
       <c r="N91">
@@ -11944,7 +14418,7 @@
         <v>-5444.39</v>
       </c>
       <c r="Y91">
-        <f>Q91/SUM(U91:V91)</f>
+        <f t="shared" ref="Y91:Y126" si="8">Q91/SUM(U91:V91)</f>
         <v>34.123312500000004</v>
       </c>
       <c r="Z91">
@@ -11978,7 +14452,7 @@
         <v>-5837.36</v>
       </c>
       <c r="AK91">
-        <f>AC91/SUM(AG91:AH91)</f>
+        <f t="shared" ref="AK91:AK126" si="9">AC91/SUM(AG91:AH91)</f>
         <v>33.849437500000001</v>
       </c>
     </row>
@@ -12014,7 +14488,7 @@
         <v>-6294.89</v>
       </c>
       <c r="M92">
-        <f>E92/SUM(I92:J92)</f>
+        <f t="shared" si="7"/>
         <v>35.864200000000004</v>
       </c>
       <c r="N92">
@@ -12048,7 +14522,7 @@
         <v>-5185.12</v>
       </c>
       <c r="Y92">
-        <f>Q92/SUM(U92:V92)</f>
+        <f t="shared" si="8"/>
         <v>33.969812499999996</v>
       </c>
       <c r="Z92">
@@ -12082,7 +14556,7 @@
         <v>-5708.24</v>
       </c>
       <c r="AK92">
-        <f>AC92/SUM(AG92:AH92)</f>
+        <f t="shared" si="9"/>
         <v>34.0093125</v>
       </c>
     </row>
@@ -12118,7 +14592,7 @@
         <v>-5498.85</v>
       </c>
       <c r="M93">
-        <f>E93/SUM(I93:J93)</f>
+        <f t="shared" si="7"/>
         <v>35.602049999999998</v>
       </c>
       <c r="N93">
@@ -12152,7 +14626,7 @@
         <v>-5344.75</v>
       </c>
       <c r="Y93">
-        <f>Q93/SUM(U93:V93)</f>
+        <f t="shared" si="8"/>
         <v>33.751374999999996</v>
       </c>
       <c r="Z93">
@@ -12186,7 +14660,7 @@
         <v>-5706.65</v>
       </c>
       <c r="AK93">
-        <f>AC93/SUM(AG93:AH93)</f>
+        <f t="shared" si="9"/>
         <v>34.158625000000001</v>
       </c>
     </row>
@@ -12222,7 +14696,7 @@
         <v>-8248.7199999999993</v>
       </c>
       <c r="M94">
-        <f>E94/SUM(I94:J94)</f>
+        <f t="shared" si="7"/>
         <v>35.107100000000003</v>
       </c>
       <c r="N94">
@@ -12256,7 +14730,7 @@
         <v>-4706.3100000000004</v>
       </c>
       <c r="Y94">
-        <f>Q94/SUM(U94:V94)</f>
+        <f t="shared" si="8"/>
         <v>33.492624999999997</v>
       </c>
       <c r="Z94">
@@ -12290,7 +14764,7 @@
         <v>-5597.71</v>
       </c>
       <c r="AK94">
-        <f>AC94/SUM(AG94:AH94)</f>
+        <f t="shared" si="9"/>
         <v>34.243499999999997</v>
       </c>
     </row>
@@ -12326,7 +14800,7 @@
         <v>-6271.09</v>
       </c>
       <c r="M95">
-        <f>E95/SUM(I95:J95)</f>
+        <f t="shared" si="7"/>
         <v>34.275999999999996</v>
       </c>
       <c r="N95">
@@ -12360,7 +14834,7 @@
         <v>-4406.75</v>
       </c>
       <c r="Y95">
-        <f>Q95/SUM(U95:V95)</f>
+        <f t="shared" si="8"/>
         <v>33.302875</v>
       </c>
       <c r="Z95">
@@ -12394,7 +14868,7 @@
         <v>-5366.83</v>
       </c>
       <c r="AK95">
-        <f>AC95/SUM(AG95:AH95)</f>
+        <f t="shared" si="9"/>
         <v>34.2034375</v>
       </c>
     </row>
@@ -12430,7 +14904,7 @@
         <v>-4853.95</v>
       </c>
       <c r="M96">
-        <f>E96/SUM(I96:J96)</f>
+        <f t="shared" si="7"/>
         <v>33.379400000000004</v>
       </c>
       <c r="N96">
@@ -12464,7 +14938,7 @@
         <v>-4839.04</v>
       </c>
       <c r="Y96">
-        <f>Q96/SUM(U96:V96)</f>
+        <f t="shared" si="8"/>
         <v>33.223500000000001</v>
       </c>
       <c r="Z96">
@@ -12498,7 +14972,7 @@
         <v>-5326.64</v>
       </c>
       <c r="AK96">
-        <f>AC96/SUM(AG96:AH96)</f>
+        <f t="shared" si="9"/>
         <v>34.045937500000001</v>
       </c>
     </row>
@@ -12534,7 +15008,7 @@
         <v>-1348.04</v>
       </c>
       <c r="M97">
-        <f>E97/SUM(I97:J97)</f>
+        <f t="shared" si="7"/>
         <v>32.610149999999997</v>
       </c>
       <c r="N97">
@@ -12568,7 +15042,7 @@
         <v>-4754.6499999999996</v>
       </c>
       <c r="Y97">
-        <f>Q97/SUM(U97:V97)</f>
+        <f t="shared" si="8"/>
         <v>33.26925</v>
       </c>
       <c r="Z97">
@@ -12602,7 +15076,7 @@
         <v>-5922.23</v>
       </c>
       <c r="AK97">
-        <f>AC97/SUM(AG97:AH97)</f>
+        <f t="shared" si="9"/>
         <v>33.78275</v>
       </c>
     </row>
@@ -12638,7 +15112,7 @@
         <v>-3912.73</v>
       </c>
       <c r="M98">
-        <f>E98/SUM(I98:J98)</f>
+        <f t="shared" si="7"/>
         <v>32.365450000000003</v>
       </c>
       <c r="N98">
@@ -12672,7 +15146,7 @@
         <v>-4440.59</v>
       </c>
       <c r="Y98">
-        <f>Q98/SUM(U98:V98)</f>
+        <f t="shared" si="8"/>
         <v>33.421750000000003</v>
       </c>
       <c r="Z98">
@@ -12706,7 +15180,7 @@
         <v>-5571.73</v>
       </c>
       <c r="AK98">
-        <f>AC98/SUM(AG98:AH98)</f>
+        <f t="shared" si="9"/>
         <v>33.451062499999999</v>
       </c>
     </row>
@@ -12742,7 +15216,7 @@
         <v>-1978.98</v>
       </c>
       <c r="M99">
-        <f>E99/SUM(I99:J99)</f>
+        <f t="shared" si="7"/>
         <v>32.456099999999999</v>
       </c>
       <c r="N99">
@@ -12776,7 +15250,7 @@
         <v>-4970.29</v>
       </c>
       <c r="Y99">
-        <f>Q99/SUM(U99:V99)</f>
+        <f t="shared" si="8"/>
         <v>33.710250000000002</v>
       </c>
       <c r="Z99">
@@ -12810,7 +15284,7 @@
         <v>-4475.47</v>
       </c>
       <c r="AK99">
-        <f>AC99/SUM(AG99:AH99)</f>
+        <f t="shared" si="9"/>
         <v>33.121124999999999</v>
       </c>
     </row>
@@ -12846,7 +15320,7 @@
         <v>-5597.07</v>
       </c>
       <c r="M100">
-        <f>E100/SUM(I100:J100)</f>
+        <f t="shared" si="7"/>
         <v>32.787199999999999</v>
       </c>
       <c r="N100">
@@ -12880,7 +15354,7 @@
         <v>-5101.6000000000004</v>
       </c>
       <c r="Y100">
-        <f>Q100/SUM(U100:V100)</f>
+        <f t="shared" si="8"/>
         <v>34.095312499999999</v>
       </c>
       <c r="Z100">
@@ -12914,7 +15388,7 @@
         <v>-5058.41</v>
       </c>
       <c r="AK100">
-        <f>AC100/SUM(AG100:AH100)</f>
+        <f t="shared" si="9"/>
         <v>32.9558125</v>
       </c>
     </row>
@@ -12950,7 +15424,7 @@
         <v>-4457.74</v>
       </c>
       <c r="M101">
-        <f>E101/SUM(I101:J101)</f>
+        <f t="shared" si="7"/>
         <v>33.2789</v>
       </c>
       <c r="N101">
@@ -12984,7 +15458,7 @@
         <v>-6744.29</v>
       </c>
       <c r="Y101">
-        <f>Q101/SUM(U101:V101)</f>
+        <f t="shared" si="8"/>
         <v>34.500937499999999</v>
       </c>
       <c r="Z101">
@@ -13018,7 +15492,7 @@
         <v>-3641.29</v>
       </c>
       <c r="AK101">
-        <f>AC101/SUM(AG101:AH101)</f>
+        <f t="shared" si="9"/>
         <v>32.948437499999997</v>
       </c>
     </row>
@@ -13054,7 +15528,7 @@
         <v>-5888.43</v>
       </c>
       <c r="M102">
-        <f>E102/SUM(I102:J102)</f>
+        <f t="shared" si="7"/>
         <v>33.890149999999998</v>
       </c>
       <c r="N102">
@@ -13088,7 +15562,7 @@
         <v>-6163.78</v>
       </c>
       <c r="Y102">
-        <f>Q102/SUM(U102:V102)</f>
+        <f t="shared" si="8"/>
         <v>34.730437500000001</v>
       </c>
       <c r="Z102">
@@ -13122,7 +15596,7 @@
         <v>-4439.1000000000004</v>
       </c>
       <c r="AK102">
-        <f>AC102/SUM(AG102:AH102)</f>
+        <f t="shared" si="9"/>
         <v>33.137187500000003</v>
       </c>
     </row>
@@ -13158,7 +15632,7 @@
         <v>-4991.41</v>
       </c>
       <c r="M103">
-        <f>E103/SUM(I103:J103)</f>
+        <f t="shared" si="7"/>
         <v>34.375149999999998</v>
       </c>
       <c r="N103">
@@ -13192,7 +15666,7 @@
         <v>-6016.33</v>
       </c>
       <c r="Y103">
-        <f>Q103/SUM(U103:V103)</f>
+        <f t="shared" si="8"/>
         <v>34.7824375</v>
       </c>
       <c r="Z103">
@@ -13226,7 +15700,7 @@
         <v>-5504.99</v>
       </c>
       <c r="AK103">
-        <f>AC103/SUM(AG103:AH103)</f>
+        <f t="shared" si="9"/>
         <v>33.413375000000002</v>
       </c>
     </row>
@@ -13262,7 +15736,7 @@
         <v>-6049.5</v>
       </c>
       <c r="M104">
-        <f>E104/SUM(I104:J104)</f>
+        <f t="shared" si="7"/>
         <v>34.628</v>
       </c>
       <c r="N104">
@@ -13296,7 +15770,7 @@
         <v>-5606.42</v>
       </c>
       <c r="Y104">
-        <f>Q104/SUM(U104:V104)</f>
+        <f t="shared" si="8"/>
         <v>34.659312499999999</v>
       </c>
       <c r="Z104">
@@ -13330,7 +15804,7 @@
         <v>-5672.17</v>
       </c>
       <c r="AK104">
-        <f>AC104/SUM(AG104:AH104)</f>
+        <f t="shared" si="9"/>
         <v>33.6700625</v>
       </c>
     </row>
@@ -13366,7 +15840,7 @@
         <v>-7882.94</v>
       </c>
       <c r="M105">
-        <f>E105/SUM(I105:J105)</f>
+        <f t="shared" si="7"/>
         <v>34.6205</v>
       </c>
       <c r="N105">
@@ -13400,7 +15874,7 @@
         <v>-5622.57</v>
       </c>
       <c r="Y105">
-        <f>Q105/SUM(U105:V105)</f>
+        <f t="shared" si="8"/>
         <v>34.407812499999999</v>
       </c>
       <c r="Z105">
@@ -13434,7 +15908,7 @@
         <v>-5691.04</v>
       </c>
       <c r="AK105">
-        <f>AC105/SUM(AG105:AH105)</f>
+        <f t="shared" si="9"/>
         <v>33.842375000000004</v>
       </c>
     </row>
@@ -13470,7 +15944,7 @@
         <v>-5501.34</v>
       </c>
       <c r="M106">
-        <f>E106/SUM(I106:J106)</f>
+        <f t="shared" si="7"/>
         <v>34.268349999999998</v>
       </c>
       <c r="N106">
@@ -13504,7 +15978,7 @@
         <v>-4865.82</v>
       </c>
       <c r="Y106">
-        <f>Q106/SUM(U106:V106)</f>
+        <f t="shared" si="8"/>
         <v>34.057562499999996</v>
       </c>
       <c r="Z106">
@@ -13538,7 +16012,7 @@
         <v>-5027.0200000000004</v>
       </c>
       <c r="AK106">
-        <f>AC106/SUM(AG106:AH106)</f>
+        <f t="shared" si="9"/>
         <v>33.948749999999997</v>
       </c>
     </row>
@@ -13574,7 +16048,7 @@
         <v>-4498.8500000000004</v>
       </c>
       <c r="M107">
-        <f>E107/SUM(I107:J107)</f>
+        <f t="shared" si="7"/>
         <v>33.827950000000001</v>
       </c>
       <c r="N107">
@@ -13608,7 +16082,7 @@
         <v>-4856.87</v>
       </c>
       <c r="Y107">
-        <f>Q107/SUM(U107:V107)</f>
+        <f t="shared" si="8"/>
         <v>33.699750000000002</v>
       </c>
       <c r="Z107">
@@ -13642,7 +16116,7 @@
         <v>-4687.22</v>
       </c>
       <c r="AK107">
-        <f>AC107/SUM(AG107:AH107)</f>
+        <f t="shared" si="9"/>
         <v>34.041937499999996</v>
       </c>
     </row>
@@ -13678,7 +16152,7 @@
         <v>-5397.61</v>
       </c>
       <c r="M108">
-        <f>E108/SUM(I108:J108)</f>
+        <f t="shared" si="7"/>
         <v>33.403700000000001</v>
       </c>
       <c r="N108">
@@ -13712,7 +16186,7 @@
         <v>-4799.32</v>
       </c>
       <c r="Y108">
-        <f>Q108/SUM(U108:V108)</f>
+        <f t="shared" si="8"/>
         <v>33.365437499999999</v>
       </c>
       <c r="Z108">
@@ -13746,7 +16220,7 @@
         <v>-5783.77</v>
       </c>
       <c r="AK108">
-        <f>AC108/SUM(AG108:AH108)</f>
+        <f t="shared" si="9"/>
         <v>34.141062499999997</v>
       </c>
     </row>
@@ -13782,7 +16256,7 @@
         <v>-6069.56</v>
       </c>
       <c r="M109">
-        <f>E109/SUM(I109:J109)</f>
+        <f t="shared" si="7"/>
         <v>33.038899999999998</v>
       </c>
       <c r="N109">
@@ -13816,7 +16290,7 @@
         <v>-4933.4399999999996</v>
       </c>
       <c r="Y109">
-        <f>Q109/SUM(U109:V109)</f>
+        <f t="shared" si="8"/>
         <v>33.122375000000005</v>
       </c>
       <c r="Z109">
@@ -13850,7 +16324,7 @@
         <v>-6274.52</v>
       </c>
       <c r="AK109">
-        <f>AC109/SUM(AG109:AH109)</f>
+        <f t="shared" si="9"/>
         <v>34.188625000000002</v>
       </c>
     </row>
@@ -13886,7 +16360,7 @@
         <v>-4534.96</v>
       </c>
       <c r="M110">
-        <f>E110/SUM(I110:J110)</f>
+        <f t="shared" si="7"/>
         <v>32.845949999999995</v>
       </c>
       <c r="N110">
@@ -13920,7 +16394,7 @@
         <v>-4340.83</v>
       </c>
       <c r="Y110">
-        <f>Q110/SUM(U110:V110)</f>
+        <f t="shared" si="8"/>
         <v>33.003999999999998</v>
       </c>
       <c r="Z110">
@@ -13954,7 +16428,7 @@
         <v>-5042.8599999999997</v>
       </c>
       <c r="AK110">
-        <f>AC110/SUM(AG110:AH110)</f>
+        <f t="shared" si="9"/>
         <v>34.184750000000001</v>
       </c>
     </row>
@@ -13990,7 +16464,7 @@
         <v>-5784.89</v>
       </c>
       <c r="M111">
-        <f>E111/SUM(I111:J111)</f>
+        <f t="shared" si="7"/>
         <v>32.878749999999997</v>
       </c>
       <c r="N111">
@@ -14024,7 +16498,7 @@
         <v>-3943.4</v>
       </c>
       <c r="Y111">
-        <f>Q111/SUM(U111:V111)</f>
+        <f t="shared" si="8"/>
         <v>33.027812500000003</v>
       </c>
       <c r="Z111">
@@ -14058,7 +16532,7 @@
         <v>-5617.75</v>
       </c>
       <c r="AK111">
-        <f>AC111/SUM(AG111:AH111)</f>
+        <f t="shared" si="9"/>
         <v>34.139499999999998</v>
       </c>
     </row>
@@ -14094,7 +16568,7 @@
         <v>-6370.91</v>
       </c>
       <c r="M112">
-        <f>E112/SUM(I112:J112)</f>
+        <f t="shared" si="7"/>
         <v>32.999850000000002</v>
       </c>
       <c r="N112">
@@ -14128,7 +16602,7 @@
         <v>-4849.76</v>
       </c>
       <c r="Y112">
-        <f>Q112/SUM(U112:V112)</f>
+        <f t="shared" si="8"/>
         <v>33.163312500000004</v>
       </c>
       <c r="Z112">
@@ -14162,7 +16636,7 @@
         <v>-6537.65</v>
       </c>
       <c r="AK112">
-        <f>AC112/SUM(AG112:AH112)</f>
+        <f t="shared" si="9"/>
         <v>34.072437499999999</v>
       </c>
     </row>
@@ -14198,7 +16672,7 @@
         <v>-5167.28</v>
       </c>
       <c r="M113">
-        <f>E113/SUM(I113:J113)</f>
+        <f t="shared" si="7"/>
         <v>33.181750000000001</v>
       </c>
       <c r="N113">
@@ -14232,7 +16706,7 @@
         <v>-4744.75</v>
       </c>
       <c r="Y113">
-        <f>Q113/SUM(U113:V113)</f>
+        <f t="shared" si="8"/>
         <v>33.383249999999997</v>
       </c>
       <c r="Z113">
@@ -14266,7 +16740,7 @@
         <v>-5081.4399999999996</v>
       </c>
       <c r="AK113">
-        <f>AC113/SUM(AG113:AH113)</f>
+        <f t="shared" si="9"/>
         <v>33.902562500000002</v>
       </c>
     </row>
@@ -14302,7 +16776,7 @@
         <v>-4682.24</v>
       </c>
       <c r="M114">
-        <f>E114/SUM(I114:J114)</f>
+        <f t="shared" si="7"/>
         <v>33.425600000000003</v>
       </c>
       <c r="N114">
@@ -14336,7 +16810,7 @@
         <v>-4805.4399999999996</v>
       </c>
       <c r="Y114">
-        <f>Q114/SUM(U114:V114)</f>
+        <f t="shared" si="8"/>
         <v>33.654312500000003</v>
       </c>
       <c r="Z114">
@@ -14370,7 +16844,7 @@
         <v>-4931.3900000000003</v>
       </c>
       <c r="AK114">
-        <f>AC114/SUM(AG114:AH114)</f>
+        <f t="shared" si="9"/>
         <v>33.694937500000002</v>
       </c>
     </row>
@@ -14406,7 +16880,7 @@
         <v>-6510.35</v>
       </c>
       <c r="M115">
-        <f>E115/SUM(I115:J115)</f>
+        <f t="shared" si="7"/>
         <v>33.588149999999999</v>
       </c>
       <c r="N115">
@@ -14440,7 +16914,7 @@
         <v>-5376.13</v>
       </c>
       <c r="Y115">
-        <f>Q115/SUM(U115:V115)</f>
+        <f t="shared" si="8"/>
         <v>33.925375000000003</v>
       </c>
       <c r="Z115">
@@ -14474,7 +16948,7 @@
         <v>-4826.38</v>
       </c>
       <c r="AK115">
-        <f>AC115/SUM(AG115:AH115)</f>
+        <f t="shared" si="9"/>
         <v>33.518000000000001</v>
       </c>
     </row>
@@ -14510,7 +16984,7 @@
         <v>-5333.24</v>
       </c>
       <c r="M116">
-        <f>E116/SUM(I116:J116)</f>
+        <f t="shared" si="7"/>
         <v>33.654650000000004</v>
       </c>
       <c r="N116">
@@ -14544,7 +17018,7 @@
         <v>-5063.29</v>
       </c>
       <c r="Y116">
-        <f>Q116/SUM(U116:V116)</f>
+        <f t="shared" si="8"/>
         <v>34.101624999999999</v>
       </c>
       <c r="Z116">
@@ -14578,7 +17052,7 @@
         <v>-5193.21</v>
       </c>
       <c r="AK116">
-        <f>AC116/SUM(AG116:AH116)</f>
+        <f t="shared" si="9"/>
         <v>33.374250000000004</v>
       </c>
     </row>
@@ -14614,7 +17088,7 @@
         <v>-8006.8</v>
       </c>
       <c r="M117">
-        <f>E117/SUM(I117:J117)</f>
+        <f t="shared" si="7"/>
         <v>33.728749999999998</v>
       </c>
       <c r="N117">
@@ -14648,7 +17122,7 @@
         <v>-5765.13</v>
       </c>
       <c r="Y117">
-        <f>Q117/SUM(U117:V117)</f>
+        <f t="shared" si="8"/>
         <v>34.187062500000003</v>
       </c>
       <c r="Z117">
@@ -14682,7 +17156,7 @@
         <v>-4415.3500000000004</v>
       </c>
       <c r="AK117">
-        <f>AC117/SUM(AG117:AH117)</f>
+        <f t="shared" si="9"/>
         <v>33.309437500000001</v>
       </c>
     </row>
@@ -14718,7 +17192,7 @@
         <v>-4719.72</v>
       </c>
       <c r="M118">
-        <f>E118/SUM(I118:J118)</f>
+        <f t="shared" si="7"/>
         <v>33.7027</v>
       </c>
       <c r="N118">
@@ -14752,7 +17226,7 @@
         <v>-5857.63</v>
       </c>
       <c r="Y118">
-        <f>Q118/SUM(U118:V118)</f>
+        <f t="shared" si="8"/>
         <v>34.152625</v>
       </c>
       <c r="Z118">
@@ -14786,7 +17260,7 @@
         <v>-5440.86</v>
       </c>
       <c r="AK118">
-        <f>AC118/SUM(AG118:AH118)</f>
+        <f t="shared" si="9"/>
         <v>33.306812499999999</v>
       </c>
     </row>
@@ -14822,7 +17296,7 @@
         <v>-6720.67</v>
       </c>
       <c r="M119">
-        <f>E119/SUM(I119:J119)</f>
+        <f t="shared" si="7"/>
         <v>33.814149999999998</v>
       </c>
       <c r="N119">
@@ -14856,7 +17330,7 @@
         <v>-5488.22</v>
       </c>
       <c r="Y119">
-        <f>Q119/SUM(U119:V119)</f>
+        <f t="shared" si="8"/>
         <v>34.013625000000005</v>
       </c>
       <c r="Z119">
@@ -14890,7 +17364,7 @@
         <v>-4509.58</v>
       </c>
       <c r="AK119">
-        <f>AC119/SUM(AG119:AH119)</f>
+        <f t="shared" si="9"/>
         <v>33.341312500000001</v>
       </c>
     </row>
@@ -14926,7 +17400,7 @@
         <v>-7139.14</v>
       </c>
       <c r="M120">
-        <f>E120/SUM(I120:J120)</f>
+        <f t="shared" si="7"/>
         <v>33.933199999999999</v>
       </c>
       <c r="N120">
@@ -14960,7 +17434,7 @@
         <v>-5430.78</v>
       </c>
       <c r="Y120">
-        <f>Q120/SUM(U120:V120)</f>
+        <f t="shared" si="8"/>
         <v>33.8410625</v>
       </c>
       <c r="Z120">
@@ -14994,7 +17468,7 @@
         <v>-4609.6899999999996</v>
       </c>
       <c r="AK120">
-        <f>AC120/SUM(AG120:AH120)</f>
+        <f t="shared" si="9"/>
         <v>33.506875000000001</v>
       </c>
     </row>
@@ -15030,7 +17504,7 @@
         <v>-6050.3</v>
       </c>
       <c r="M121">
-        <f>E121/SUM(I121:J121)</f>
+        <f t="shared" si="7"/>
         <v>33.910049999999998</v>
       </c>
       <c r="N121">
@@ -15064,7 +17538,7 @@
         <v>-6244.61</v>
       </c>
       <c r="Y121">
-        <f>Q121/SUM(U121:V121)</f>
+        <f t="shared" si="8"/>
         <v>33.638437500000002</v>
       </c>
       <c r="Z121">
@@ -15098,7 +17572,7 @@
         <v>-5010.33</v>
       </c>
       <c r="AK121">
-        <f>AC121/SUM(AG121:AH121)</f>
+        <f t="shared" si="9"/>
         <v>33.730125000000001</v>
       </c>
     </row>
@@ -15134,7 +17608,7 @@
         <v>-7080.22</v>
       </c>
       <c r="M122">
-        <f>E122/SUM(I122:J122)</f>
+        <f t="shared" si="7"/>
         <v>33.77955</v>
       </c>
       <c r="N122">
@@ -15168,7 +17642,7 @@
         <v>-5771.94</v>
       </c>
       <c r="Y122">
-        <f>Q122/SUM(U122:V122)</f>
+        <f t="shared" si="8"/>
         <v>33.477874999999997</v>
       </c>
       <c r="Z122">
@@ -15202,7 +17676,7 @@
         <v>-5371.26</v>
       </c>
       <c r="AK122">
-        <f>AC122/SUM(AG122:AH122)</f>
+        <f t="shared" si="9"/>
         <v>33.90025</v>
       </c>
     </row>
@@ -15238,7 +17712,7 @@
         <v>-5490.14</v>
       </c>
       <c r="M123">
-        <f>E123/SUM(I123:J123)</f>
+        <f t="shared" si="7"/>
         <v>33.608350000000002</v>
       </c>
       <c r="N123">
@@ -15272,7 +17746,7 @@
         <v>-4739.67</v>
       </c>
       <c r="Y123">
-        <f>Q123/SUM(U123:V123)</f>
+        <f t="shared" si="8"/>
         <v>33.380812500000005</v>
       </c>
       <c r="Z123">
@@ -15306,7 +17780,7 @@
         <v>-6062.23</v>
       </c>
       <c r="AK123">
-        <f>AC123/SUM(AG123:AH123)</f>
+        <f t="shared" si="9"/>
         <v>33.9936875</v>
       </c>
     </row>
@@ -15342,7 +17816,7 @@
         <v>-5200.34</v>
       </c>
       <c r="M124">
-        <f>E124/SUM(I124:J124)</f>
+        <f t="shared" si="7"/>
         <v>33.390450000000001</v>
       </c>
       <c r="N124">
@@ -15376,7 +17850,7 @@
         <v>-5228.6499999999996</v>
       </c>
       <c r="Y124">
-        <f>Q124/SUM(U124:V124)</f>
+        <f t="shared" si="8"/>
         <v>33.356625000000001</v>
       </c>
       <c r="Z124">
@@ -15410,7 +17884,7 @@
         <v>-5384.92</v>
       </c>
       <c r="AK124">
-        <f>AC124/SUM(AG124:AH124)</f>
+        <f t="shared" si="9"/>
         <v>33.992874999999998</v>
       </c>
     </row>
@@ -15446,7 +17920,7 @@
         <v>-5904.14</v>
       </c>
       <c r="M125">
-        <f>E125/SUM(I125:J125)</f>
+        <f t="shared" si="7"/>
         <v>33.062750000000001</v>
       </c>
       <c r="N125">
@@ -15480,7 +17954,7 @@
         <v>-4991.25</v>
       </c>
       <c r="Y125">
-        <f>Q125/SUM(U125:V125)</f>
+        <f t="shared" si="8"/>
         <v>33.394437500000002</v>
       </c>
       <c r="Z125">
@@ -15514,7 +17988,7 @@
         <v>-5483.54</v>
       </c>
       <c r="AK125">
-        <f>AC125/SUM(AG125:AH125)</f>
+        <f t="shared" si="9"/>
         <v>33.894125000000003</v>
       </c>
     </row>
@@ -15550,7 +18024,7 @@
         <v>-6436.99</v>
       </c>
       <c r="M126">
-        <f>E126/SUM(I126:J126)</f>
+        <f t="shared" si="7"/>
         <v>32.7943</v>
       </c>
       <c r="N126">
@@ -15584,7 +18058,7 @@
         <v>-4979.87</v>
       </c>
       <c r="Y126">
-        <f>Q126/SUM(U126:V126)</f>
+        <f t="shared" si="8"/>
         <v>33.466000000000001</v>
       </c>
       <c r="Z126">
@@ -15618,7 +18092,7 @@
         <v>-4917.7299999999996</v>
       </c>
       <c r="AK126">
-        <f>AC126/SUM(AG126:AH126)</f>
+        <f t="shared" si="9"/>
         <v>33.717687500000004</v>
       </c>
     </row>
@@ -15788,6 +18262,2836 @@
       <c r="AC136">
         <f>STDEV(AC131:AC133)</f>
         <v>4.1583067969610285E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A437A940-1343-5643-9D4F-169D8F4C58F7}">
+  <dimension ref="B5:AN67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="5" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="P10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R10" t="s">
+        <v>73</v>
+      </c>
+      <c r="S10" t="s">
+        <v>68</v>
+      </c>
+      <c r="V10" t="s">
+        <v>60</v>
+      </c>
+      <c r="W10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>1200</v>
+      </c>
+      <c r="C11">
+        <f>2.03-0.000505*B11</f>
+        <v>1.4239999999999999</v>
+      </c>
+      <c r="D11">
+        <v>1.4521982984824864</v>
+      </c>
+      <c r="E11">
+        <v>1.4201392391206853</v>
+      </c>
+      <c r="F11">
+        <v>1.4469897432071506</v>
+      </c>
+      <c r="G11">
+        <v>1.4218075477230747</v>
+      </c>
+      <c r="H11">
+        <v>1.4380980575271523</v>
+      </c>
+      <c r="I11">
+        <f>MAX(D11:H11)-MIN(D11:H11)</f>
+        <v>3.205905936180109E-2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>60</v>
+      </c>
+      <c r="P11">
+        <v>958.14</v>
+      </c>
+      <c r="Q11" s="4">
+        <f>P11/$P$16</f>
+        <v>0.35751492537313434</v>
+      </c>
+      <c r="R11" s="4">
+        <f>1/Q11</f>
+        <v>2.7970860208320287</v>
+      </c>
+      <c r="S11" s="4">
+        <v>66.500148797145641</v>
+      </c>
+      <c r="U11">
+        <v>1200</v>
+      </c>
+      <c r="V11">
+        <v>0.74217781689879514</v>
+      </c>
+      <c r="W11">
+        <v>0.77195398536684023</v>
+      </c>
+      <c r="X11">
+        <v>0.7551706534642697</v>
+      </c>
+      <c r="Y11">
+        <v>0.77498233040286679</v>
+      </c>
+      <c r="Z11">
+        <v>0.82105716035738963</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>1300</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:C14" si="0">2.03-0.000505*B12</f>
+        <v>1.3734999999999997</v>
+      </c>
+      <c r="D12">
+        <v>1.4072080172825043</v>
+      </c>
+      <c r="E12">
+        <v>1.3815717960818399</v>
+      </c>
+      <c r="F12">
+        <v>1.3966767449312834</v>
+      </c>
+      <c r="G12">
+        <v>1.37530193246221</v>
+      </c>
+      <c r="H12">
+        <v>1.3937335414873917</v>
+      </c>
+      <c r="I12">
+        <f t="shared" ref="I12:I14" si="1">MAX(D12:H12)-MIN(D12:H12)</f>
+        <v>3.1906084820294334E-2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>61</v>
+      </c>
+      <c r="P12">
+        <v>681.91300000000001</v>
+      </c>
+      <c r="Q12" s="4">
+        <f>P12/$P$16</f>
+        <v>0.25444514925373135</v>
+      </c>
+      <c r="R12" s="4">
+        <f t="shared" ref="R12:R16" si="2">1/Q12</f>
+        <v>3.9301201179622618</v>
+      </c>
+      <c r="S12" s="4">
+        <v>67.79126301354583</v>
+      </c>
+      <c r="U12">
+        <v>1300</v>
+      </c>
+      <c r="V12">
+        <v>0.68435402454914762</v>
+      </c>
+      <c r="W12">
+        <v>0.63210645684103528</v>
+      </c>
+      <c r="X12">
+        <v>0.67726541896316084</v>
+      </c>
+      <c r="Y12">
+        <v>0.60724491766366162</v>
+      </c>
+      <c r="Z12">
+        <v>0.6562868340985637</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>1400</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1.3229999999999997</v>
+      </c>
+      <c r="D13">
+        <v>1.3646263311944169</v>
+      </c>
+      <c r="E13">
+        <v>1.3349550283232501</v>
+      </c>
+      <c r="F13">
+        <v>1.351633331649178</v>
+      </c>
+      <c r="G13">
+        <v>1.3339748868159742</v>
+      </c>
+      <c r="H13">
+        <v>1.3492239066994554</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>3.0651444378442694E-2</v>
+      </c>
+      <c r="O13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P13">
+        <v>482.40699999999998</v>
+      </c>
+      <c r="Q13" s="4">
+        <f>P13/$P$16</f>
+        <v>0.18000261194029851</v>
+      </c>
+      <c r="R13" s="4">
+        <f t="shared" si="2"/>
+        <v>5.555474941284019</v>
+      </c>
+      <c r="S13" s="4">
+        <v>68.755392542124341</v>
+      </c>
+      <c r="U13">
+        <v>1400</v>
+      </c>
+      <c r="V13">
+        <v>0.54371702356252105</v>
+      </c>
+      <c r="W13">
+        <v>0.54084458290065762</v>
+      </c>
+      <c r="X13">
+        <v>0.53686836095163137</v>
+      </c>
+      <c r="Y13">
+        <v>0.58232571573653724</v>
+      </c>
+      <c r="Z13">
+        <v>0.55421865699518158</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>1500</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>1.2724999999999997</v>
+      </c>
+      <c r="D14">
+        <v>1.3253968124454378</v>
+      </c>
+      <c r="E14">
+        <v>1.2852095195496671</v>
+      </c>
+      <c r="F14">
+        <v>1.3003403263059448</v>
+      </c>
+      <c r="G14">
+        <v>1.2865074461928288</v>
+      </c>
+      <c r="H14">
+        <v>1.3083489522164848</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>4.0187292895770721E-2</v>
+      </c>
+      <c r="O14" t="s">
+        <v>63</v>
+      </c>
+      <c r="P14">
+        <v>1477.75</v>
+      </c>
+      <c r="Q14" s="4">
+        <f>P14/$P$16</f>
+        <v>0.55139925373134324</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="2"/>
+        <v>1.8135679242091018</v>
+      </c>
+      <c r="S14" s="4">
+        <v>66.835690415927758</v>
+      </c>
+      <c r="U14">
+        <v>1500</v>
+      </c>
+      <c r="V14">
+        <v>0.46281511924431556</v>
+      </c>
+      <c r="W14">
+        <v>0.49396522682389249</v>
+      </c>
+      <c r="X14">
+        <v>0.50648298217179899</v>
+      </c>
+      <c r="Y14">
+        <v>0.50545537991542722</v>
+      </c>
+      <c r="Z14">
+        <v>0.49782599388470555</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <f>(D11-C11)/C11</f>
+        <v>1.9802175900622509E-2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15">
+        <v>2360.5</v>
+      </c>
+      <c r="Q15" s="4">
+        <f>P15/$P$16</f>
+        <v>0.88078358208955221</v>
+      </c>
+      <c r="R15" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1353526795170514</v>
+      </c>
+      <c r="S15" s="4">
+        <v>67.472319614814538</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <f t="shared" ref="D16:D18" si="3">(D12-C12)/C12</f>
+        <v>2.4541694417549775E-2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>71</v>
+      </c>
+      <c r="P16">
+        <f>2.68*1000</f>
+        <v>2680</v>
+      </c>
+      <c r="Q16" s="4">
+        <f>P16/$P$16</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <f t="shared" si="3"/>
+        <v>3.1463591227828554E-2</v>
+      </c>
+      <c r="V17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <f>(D14-C14)/C14</f>
+        <v>4.1569204279322675E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="F19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>6.94</v>
+      </c>
+      <c r="H19">
+        <v>39.097999999999999</v>
+      </c>
+      <c r="I19">
+        <v>22.99</v>
+      </c>
+      <c r="J19">
+        <v>35.450000000000003</v>
+      </c>
+      <c r="U19">
+        <v>1200</v>
+      </c>
+      <c r="V19">
+        <v>600000</v>
+      </c>
+      <c r="W19">
+        <v>1.47102</v>
+      </c>
+      <c r="X19">
+        <v>0.69268099999999999</v>
+      </c>
+      <c r="Y19">
+        <v>1376.19</v>
+      </c>
+      <c r="AB19">
+        <v>1200</v>
+      </c>
+      <c r="AC19">
+        <v>600000</v>
+      </c>
+      <c r="AD19">
+        <v>1.47235</v>
+      </c>
+      <c r="AE19">
+        <v>0.65113799999999999</v>
+      </c>
+      <c r="AF19">
+        <v>1293.25</v>
+      </c>
+      <c r="AI19">
+        <v>1200</v>
+      </c>
+      <c r="AJ19">
+        <v>600000</v>
+      </c>
+      <c r="AK19">
+        <v>1.4713799999999999</v>
+      </c>
+      <c r="AL19">
+        <v>0.66652</v>
+      </c>
+      <c r="AM19">
+        <v>1324.13</v>
+      </c>
+    </row>
+    <row r="20" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20">
+        <v>700000</v>
+      </c>
+      <c r="W20">
+        <v>1.46997</v>
+      </c>
+      <c r="X20">
+        <v>0.64649299999999998</v>
+      </c>
+      <c r="Y20">
+        <v>1284.76</v>
+      </c>
+      <c r="AC20">
+        <v>700000</v>
+      </c>
+      <c r="AD20">
+        <v>1.4713099999999999</v>
+      </c>
+      <c r="AE20">
+        <v>0.65574299999999996</v>
+      </c>
+      <c r="AF20">
+        <v>1302.78</v>
+      </c>
+      <c r="AJ20">
+        <v>700000</v>
+      </c>
+      <c r="AK20">
+        <v>1.47159</v>
+      </c>
+      <c r="AL20">
+        <v>0.57474700000000001</v>
+      </c>
+      <c r="AM20">
+        <v>1141.8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="K21" t="s">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>19</v>
+      </c>
+      <c r="N21" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>20</v>
+      </c>
+      <c r="V21">
+        <v>800000</v>
+      </c>
+      <c r="W21">
+        <v>1.4703200000000001</v>
+      </c>
+      <c r="X21">
+        <v>0.66824099999999997</v>
+      </c>
+      <c r="Y21">
+        <v>1327.91</v>
+      </c>
+      <c r="AC21">
+        <v>800000</v>
+      </c>
+      <c r="AD21">
+        <v>1.4722999999999999</v>
+      </c>
+      <c r="AE21">
+        <v>0.763961</v>
+      </c>
+      <c r="AF21">
+        <v>1517.45</v>
+      </c>
+      <c r="AJ21">
+        <v>800000</v>
+      </c>
+      <c r="AK21">
+        <v>1.4714</v>
+      </c>
+      <c r="AL21">
+        <v>0.57133400000000001</v>
+      </c>
+      <c r="AM21">
+        <v>1135.01</v>
+      </c>
+    </row>
+    <row r="22" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>100000</v>
+      </c>
+      <c r="C22">
+        <v>1199.51</v>
+      </c>
+      <c r="D22">
+        <v>-2933.16</v>
+      </c>
+      <c r="E22">
+        <v>53422.9</v>
+      </c>
+      <c r="F22">
+        <v>-44.899900000000002</v>
+      </c>
+      <c r="G22">
+        <v>268</v>
+      </c>
+      <c r="H22">
+        <v>266</v>
+      </c>
+      <c r="I22">
+        <v>266</v>
+      </c>
+      <c r="J22">
+        <v>800</v>
+      </c>
+      <c r="K22">
+        <f>G22*$G$19+H22*$H$19+I22*$I$19+J22*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L22">
+        <f>(K22*1.66E-24)/(E22*1E-24)</f>
+        <v>1.4521982984824864</v>
+      </c>
+      <c r="N22">
+        <v>937.42100000000005</v>
+      </c>
+      <c r="O22">
+        <f>AVERAGE(N22:N25)</f>
+        <v>958.14</v>
+      </c>
+      <c r="Q22">
+        <f>D22+(1.5*(0.000086173)*C22*SUM(G22:J22))</f>
+        <v>-2685.0830994479998</v>
+      </c>
+      <c r="R22" cm="1">
+        <f t="array" ref="R22:S22">LINEST(Q22:Q25,C22:C25)</f>
+        <v>0.5514540633336994</v>
+      </c>
+      <c r="S22">
+        <v>-3345.9168993249859</v>
+      </c>
+      <c r="V22">
+        <v>900000</v>
+      </c>
+      <c r="W22">
+        <v>1.47194</v>
+      </c>
+      <c r="X22">
+        <v>0.64171900000000004</v>
+      </c>
+      <c r="Y22">
+        <v>1274.72</v>
+      </c>
+      <c r="AC22">
+        <v>900000</v>
+      </c>
+      <c r="AD22">
+        <v>1.4718199999999999</v>
+      </c>
+      <c r="AE22">
+        <v>0.61241699999999999</v>
+      </c>
+      <c r="AF22">
+        <v>1216.45</v>
+      </c>
+      <c r="AJ22">
+        <v>900000</v>
+      </c>
+      <c r="AK22">
+        <v>1.4718599999999999</v>
+      </c>
+      <c r="AL22">
+        <v>0.65232900000000005</v>
+      </c>
+      <c r="AM22">
+        <v>1295.8</v>
+      </c>
+    </row>
+    <row r="23" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>100000</v>
+      </c>
+      <c r="C23">
+        <v>1298.06</v>
+      </c>
+      <c r="D23">
+        <v>-2897.8</v>
+      </c>
+      <c r="E23">
+        <v>55130.9</v>
+      </c>
+      <c r="F23">
+        <v>-75.903999999999996</v>
+      </c>
+      <c r="G23">
+        <v>268</v>
+      </c>
+      <c r="H23">
+        <v>266</v>
+      </c>
+      <c r="I23">
+        <v>266</v>
+      </c>
+      <c r="J23">
+        <v>800</v>
+      </c>
+      <c r="K23">
+        <f>G23*$G$19+H23*$H$19+I23*$I$19+J23*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L23">
+        <f t="shared" ref="L23:L25" si="4">(K23*1.66E-24)/(E23*1E-24)</f>
+        <v>1.4072080172825043</v>
+      </c>
+      <c r="N23">
+        <v>948.71</v>
+      </c>
+      <c r="O23" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" ref="Q23:Q25" si="5">D23+(1.5*(0.000086173)*C23*SUM(G23:J23))</f>
+        <v>-2629.3414614880003</v>
+      </c>
+      <c r="R23">
+        <f>R22/SUM(G22:I22)*(1.602E-19)*(6.022E+23)</f>
+        <v>66.500148797145641</v>
+      </c>
+      <c r="S23" t="s">
+        <v>66</v>
+      </c>
+      <c r="V23">
+        <v>1000000</v>
+      </c>
+      <c r="W23">
+        <v>1.47278</v>
+      </c>
+      <c r="X23">
+        <v>0.59826100000000004</v>
+      </c>
+      <c r="Y23">
+        <v>1188.18</v>
+      </c>
+      <c r="Z23">
+        <f>1000/AVERAGE(Y19:Y23)</f>
+        <v>0.77498233040286679</v>
+      </c>
+      <c r="AC23">
+        <v>1000000</v>
+      </c>
+      <c r="AD23">
+        <v>1.4721500000000001</v>
+      </c>
+      <c r="AE23">
+        <v>0.70836100000000002</v>
+      </c>
+      <c r="AF23">
+        <v>1407</v>
+      </c>
+      <c r="AG23">
+        <f>1000/AVERAGE(AF19:AF23)</f>
+        <v>0.74217781689879514</v>
+      </c>
+      <c r="AJ23">
+        <v>1000000</v>
+      </c>
+      <c r="AK23">
+        <v>1.47143</v>
+      </c>
+      <c r="AL23">
+        <v>0.60044799999999998</v>
+      </c>
+      <c r="AM23">
+        <v>1192.97</v>
+      </c>
+      <c r="AN23">
+        <f>1000/AVERAGE(AM19:AM23)</f>
+        <v>0.82105716035738963</v>
+      </c>
+    </row>
+    <row r="24" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>100000</v>
+      </c>
+      <c r="C24">
+        <v>1401.13</v>
+      </c>
+      <c r="D24">
+        <v>-2862.63</v>
+      </c>
+      <c r="E24">
+        <v>56851.199999999997</v>
+      </c>
+      <c r="F24">
+        <v>-8.3133300000000006</v>
+      </c>
+      <c r="G24">
+        <v>268</v>
+      </c>
+      <c r="H24">
+        <v>266</v>
+      </c>
+      <c r="I24">
+        <v>266</v>
+      </c>
+      <c r="J24">
+        <v>800</v>
+      </c>
+      <c r="K24">
+        <f>G24*$G$19+H24*$H$19+I24*$I$19+J24*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="4"/>
+        <v>1.3646263311944169</v>
+      </c>
+      <c r="N24">
+        <v>968.99900000000002</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="5"/>
+        <v>-2572.8550188240001</v>
+      </c>
+    </row>
+    <row r="25" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>100000</v>
+      </c>
+      <c r="C25">
+        <v>1500.51</v>
+      </c>
+      <c r="D25">
+        <v>-2829.3</v>
+      </c>
+      <c r="E25">
+        <v>58533.9</v>
+      </c>
+      <c r="F25">
+        <v>56.941299999999998</v>
+      </c>
+      <c r="G25">
+        <v>268</v>
+      </c>
+      <c r="H25">
+        <v>266</v>
+      </c>
+      <c r="I25">
+        <v>266</v>
+      </c>
+      <c r="J25">
+        <v>800</v>
+      </c>
+      <c r="K25">
+        <f>G25*$G$19+H25*$H$19+I25*$I$19+J25*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="4"/>
+        <v>1.3253968124454378</v>
+      </c>
+      <c r="N25">
+        <v>977.43</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="5"/>
+        <v>-2518.9717242480001</v>
+      </c>
+      <c r="U25">
+        <v>1300</v>
+      </c>
+      <c r="V25">
+        <v>600000</v>
+      </c>
+      <c r="W25">
+        <v>1.42831</v>
+      </c>
+      <c r="X25">
+        <v>0.82969199999999999</v>
+      </c>
+      <c r="Y25">
+        <v>1664.77</v>
+      </c>
+      <c r="AB25">
+        <v>1300</v>
+      </c>
+      <c r="AC25">
+        <v>600000</v>
+      </c>
+      <c r="AD25">
+        <v>1.42761</v>
+      </c>
+      <c r="AE25">
+        <v>0.741116</v>
+      </c>
+      <c r="AF25">
+        <v>1487.28</v>
+      </c>
+      <c r="AI25">
+        <v>1300</v>
+      </c>
+      <c r="AJ25">
+        <v>600000</v>
+      </c>
+      <c r="AK25">
+        <v>1.42927</v>
+      </c>
+      <c r="AL25">
+        <v>0.83113300000000001</v>
+      </c>
+      <c r="AM25">
+        <v>1667.29</v>
+      </c>
+    </row>
+    <row r="26" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="V26">
+        <v>700000</v>
+      </c>
+      <c r="W26">
+        <v>1.42642</v>
+      </c>
+      <c r="X26">
+        <v>0.78553499999999998</v>
+      </c>
+      <c r="Y26">
+        <v>1576.81</v>
+      </c>
+      <c r="AC26">
+        <v>700000</v>
+      </c>
+      <c r="AD26">
+        <v>1.42902</v>
+      </c>
+      <c r="AE26">
+        <v>0.74786699999999995</v>
+      </c>
+      <c r="AF26">
+        <v>1500.31</v>
+      </c>
+      <c r="AJ26">
+        <v>700000</v>
+      </c>
+      <c r="AK26">
+        <v>1.4296199999999999</v>
+      </c>
+      <c r="AL26">
+        <v>0.70822399999999996</v>
+      </c>
+      <c r="AM26">
+        <v>1420.55</v>
+      </c>
+    </row>
+    <row r="27" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="V27">
+        <v>800000</v>
+      </c>
+      <c r="W27">
+        <v>1.42909</v>
+      </c>
+      <c r="X27">
+        <v>0.71484599999999998</v>
+      </c>
+      <c r="Y27">
+        <v>1434.07</v>
+      </c>
+      <c r="AC27">
+        <v>800000</v>
+      </c>
+      <c r="AD27">
+        <v>1.4274100000000001</v>
+      </c>
+      <c r="AE27">
+        <v>0.71874400000000005</v>
+      </c>
+      <c r="AF27">
+        <v>1442.43</v>
+      </c>
+      <c r="AJ27">
+        <v>800000</v>
+      </c>
+      <c r="AK27">
+        <v>1.4278900000000001</v>
+      </c>
+      <c r="AL27">
+        <v>0.69199100000000002</v>
+      </c>
+      <c r="AM27">
+        <v>1388.62</v>
+      </c>
+    </row>
+    <row r="28" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="V28">
+        <v>900000</v>
+      </c>
+      <c r="W28">
+        <v>1.42709</v>
+      </c>
+      <c r="X28">
+        <v>0.84440599999999999</v>
+      </c>
+      <c r="Y28">
+        <v>1694.76</v>
+      </c>
+      <c r="AC28">
+        <v>900000</v>
+      </c>
+      <c r="AD28">
+        <v>1.42849</v>
+      </c>
+      <c r="AE28">
+        <v>0.66290800000000005</v>
+      </c>
+      <c r="AF28">
+        <v>1329.98</v>
+      </c>
+      <c r="AJ28">
+        <v>900000</v>
+      </c>
+      <c r="AK28">
+        <v>1.4283399999999999</v>
+      </c>
+      <c r="AL28">
+        <v>0.76108600000000004</v>
+      </c>
+      <c r="AM28">
+        <v>1526.97</v>
+      </c>
+    </row>
+    <row r="29" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>100000</v>
+      </c>
+      <c r="C29">
+        <v>1201.06</v>
+      </c>
+      <c r="D29">
+        <v>-2922.67</v>
+      </c>
+      <c r="E29">
+        <v>54628.9</v>
+      </c>
+      <c r="F29">
+        <v>-8.7104999999999997</v>
+      </c>
+      <c r="G29">
+        <v>268</v>
+      </c>
+      <c r="H29">
+        <v>266</v>
+      </c>
+      <c r="I29">
+        <v>266</v>
+      </c>
+      <c r="J29">
+        <v>800</v>
+      </c>
+      <c r="K29">
+        <f>G29*$G$19+H29*$H$19+I29*$I$19+J29*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L29">
+        <f>(K29*1.66E-24)/(E29*1E-24)</f>
+        <v>1.4201392391206853</v>
+      </c>
+      <c r="N29">
+        <v>678.24400000000003</v>
+      </c>
+      <c r="O29">
+        <f>AVERAGE(N29:N32)</f>
+        <v>681.91300000000001</v>
+      </c>
+      <c r="Q29">
+        <f>D29+(1.5*(0.000086173)*C29*SUM(G29:J29))</f>
+        <v>-2674.2725358880002</v>
+      </c>
+      <c r="R29" cm="1">
+        <f t="array" ref="R29:S29">LINEST(Q29:Q32,C29:C32)</f>
+        <v>0.56216065863822517</v>
+      </c>
+      <c r="S29">
+        <v>-3350.2790342525441</v>
+      </c>
+      <c r="V29">
+        <v>1000000</v>
+      </c>
+      <c r="W29">
+        <v>1.42841</v>
+      </c>
+      <c r="X29">
+        <v>0.92877500000000002</v>
+      </c>
+      <c r="Y29">
+        <v>1863.5</v>
+      </c>
+      <c r="Z29">
+        <f>1000/AVERAGE(Y25:Y29)</f>
+        <v>0.60724491766366162</v>
+      </c>
+      <c r="AC29">
+        <v>1000000</v>
+      </c>
+      <c r="AD29">
+        <v>1.4286700000000001</v>
+      </c>
+      <c r="AE29">
+        <v>0.77065099999999997</v>
+      </c>
+      <c r="AF29">
+        <v>1546.16</v>
+      </c>
+      <c r="AG29">
+        <f>1000/AVERAGE(AF25:AF29)</f>
+        <v>0.68435402454914762</v>
+      </c>
+      <c r="AJ29">
+        <v>1000000</v>
+      </c>
+      <c r="AK29">
+        <v>1.4266399999999999</v>
+      </c>
+      <c r="AL29">
+        <v>0.80471199999999998</v>
+      </c>
+      <c r="AM29">
+        <v>1615.19</v>
+      </c>
+      <c r="AN29">
+        <f>1000/AVERAGE(AM25:AM29)</f>
+        <v>0.6562868340985637</v>
+      </c>
+    </row>
+    <row r="30" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>100000</v>
+      </c>
+      <c r="C30">
+        <v>1299.7</v>
+      </c>
+      <c r="D30">
+        <v>-2889.31</v>
+      </c>
+      <c r="E30">
+        <v>56153.9</v>
+      </c>
+      <c r="F30">
+        <v>49.739699999999999</v>
+      </c>
+      <c r="G30">
+        <v>268</v>
+      </c>
+      <c r="H30">
+        <v>266</v>
+      </c>
+      <c r="I30">
+        <v>266</v>
+      </c>
+      <c r="J30">
+        <v>800</v>
+      </c>
+      <c r="K30">
+        <f>G30*$G$19+H30*$H$19+I30*$I$19+J30*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L30">
+        <f t="shared" ref="L30:L32" si="6">(K30*1.66E-24)/(E30*1E-24)</f>
+        <v>1.3815717960818399</v>
+      </c>
+      <c r="N30">
+        <v>666.56299999999999</v>
+      </c>
+      <c r="O30" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" ref="Q30:Q32" si="7">D30+(1.5*(0.000086173)*C30*SUM(G30:J30))</f>
+        <v>-2620.5122845599999</v>
+      </c>
+      <c r="R30">
+        <f>R29/SUM(G29:I29)*(1.602E-19)*(6.022E+23)</f>
+        <v>67.79126301354583</v>
+      </c>
+      <c r="S30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>100000</v>
+      </c>
+      <c r="C31">
+        <v>1398.64</v>
+      </c>
+      <c r="D31">
+        <v>-2853.96</v>
+      </c>
+      <c r="E31">
+        <v>58114.8</v>
+      </c>
+      <c r="F31">
+        <v>-7.7317200000000001</v>
+      </c>
+      <c r="G31">
+        <v>268</v>
+      </c>
+      <c r="H31">
+        <v>266</v>
+      </c>
+      <c r="I31">
+        <v>266</v>
+      </c>
+      <c r="J31">
+        <v>800</v>
+      </c>
+      <c r="K31">
+        <f>G31*$G$19+H31*$H$19+I31*$I$19+J31*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="6"/>
+        <v>1.3349550283232501</v>
+      </c>
+      <c r="N31">
+        <v>682.05100000000004</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="7"/>
+        <v>-2564.699988672</v>
+      </c>
+      <c r="U31">
+        <v>1400</v>
+      </c>
+      <c r="V31">
+        <v>600000</v>
+      </c>
+      <c r="W31">
+        <v>1.3857200000000001</v>
+      </c>
+      <c r="X31">
+        <v>0.93722099999999997</v>
+      </c>
+      <c r="Y31">
+        <v>1899.49</v>
+      </c>
+      <c r="AB31">
+        <v>1400</v>
+      </c>
+      <c r="AC31">
+        <v>600000</v>
+      </c>
+      <c r="AD31">
+        <v>1.3859900000000001</v>
+      </c>
+      <c r="AE31">
+        <v>0.81157599999999996</v>
+      </c>
+      <c r="AF31">
+        <v>1644.81</v>
+      </c>
+      <c r="AI31">
+        <v>1400</v>
+      </c>
+      <c r="AJ31">
+        <v>600000</v>
+      </c>
+      <c r="AK31">
+        <v>1.3855999999999999</v>
+      </c>
+      <c r="AL31">
+        <v>0.92325800000000002</v>
+      </c>
+      <c r="AM31">
+        <v>1871.34</v>
+      </c>
+    </row>
+    <row r="32" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>100000</v>
+      </c>
+      <c r="C32">
+        <v>1500.63</v>
+      </c>
+      <c r="D32">
+        <v>-2816.3</v>
+      </c>
+      <c r="E32">
+        <v>60364.2</v>
+      </c>
+      <c r="F32">
+        <v>-65.107600000000005</v>
+      </c>
+      <c r="G32">
+        <v>268</v>
+      </c>
+      <c r="H32">
+        <v>266</v>
+      </c>
+      <c r="I32">
+        <v>266</v>
+      </c>
+      <c r="J32">
+        <v>800</v>
+      </c>
+      <c r="K32">
+        <f>G32*$G$19+H32*$H$19+I32*$I$19+J32*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="6"/>
+        <v>1.2852095195496671</v>
+      </c>
+      <c r="N32">
+        <v>700.79399999999998</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="7"/>
+        <v>-2505.9469064240002</v>
+      </c>
+      <c r="V32">
+        <v>700000</v>
+      </c>
+      <c r="W32">
+        <v>1.38558</v>
+      </c>
+      <c r="X32">
+        <v>0.85501000000000005</v>
+      </c>
+      <c r="Y32">
+        <v>1732.99</v>
+      </c>
+      <c r="AC32">
+        <v>700000</v>
+      </c>
+      <c r="AD32">
+        <v>1.3859600000000001</v>
+      </c>
+      <c r="AE32">
+        <v>0.86763400000000002</v>
+      </c>
+      <c r="AF32">
+        <v>1758.38</v>
+      </c>
+      <c r="AJ32">
+        <v>700000</v>
+      </c>
+      <c r="AK32">
+        <v>1.38486</v>
+      </c>
+      <c r="AL32">
+        <v>0.87117599999999995</v>
+      </c>
+      <c r="AM32">
+        <v>1766.04</v>
+      </c>
+    </row>
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="V33">
+        <v>800000</v>
+      </c>
+      <c r="W33">
+        <v>1.38598</v>
+      </c>
+      <c r="X33">
+        <v>0.88384300000000005</v>
+      </c>
+      <c r="Y33">
+        <v>1791.28</v>
+      </c>
+      <c r="AC33">
+        <v>800000</v>
+      </c>
+      <c r="AD33">
+        <v>1.38419</v>
+      </c>
+      <c r="AE33">
+        <v>0.91553399999999996</v>
+      </c>
+      <c r="AF33">
+        <v>1856.22</v>
+      </c>
+      <c r="AJ33">
+        <v>800000</v>
+      </c>
+      <c r="AK33">
+        <v>1.38561</v>
+      </c>
+      <c r="AL33">
+        <v>0.90397000000000005</v>
+      </c>
+      <c r="AM33">
+        <v>1832.15</v>
+      </c>
+    </row>
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="V34">
+        <v>900000</v>
+      </c>
+      <c r="W34">
+        <v>1.3857999999999999</v>
+      </c>
+      <c r="X34">
+        <v>0.68993400000000005</v>
+      </c>
+      <c r="Y34">
+        <v>1398.37</v>
+      </c>
+      <c r="AC34">
+        <v>900000</v>
+      </c>
+      <c r="AD34">
+        <v>1.38442</v>
+      </c>
+      <c r="AE34">
+        <v>0.96691300000000002</v>
+      </c>
+      <c r="AF34">
+        <v>1960.41</v>
+      </c>
+      <c r="AJ34">
+        <v>900000</v>
+      </c>
+      <c r="AK34">
+        <v>1.3859600000000001</v>
+      </c>
+      <c r="AL34">
+        <v>0.878525</v>
+      </c>
+      <c r="AM34">
+        <v>1780.48</v>
+      </c>
+    </row>
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="V35">
+        <v>1000000</v>
+      </c>
+      <c r="W35">
+        <v>1.3854200000000001</v>
+      </c>
+      <c r="X35">
+        <v>0.87032100000000001</v>
+      </c>
+      <c r="Y35">
+        <v>1764.13</v>
+      </c>
+      <c r="Z35">
+        <f>1000/AVERAGE(Y31:Y35)</f>
+        <v>0.58232571573653724</v>
+      </c>
+      <c r="AC35">
+        <v>1000000</v>
+      </c>
+      <c r="AD35">
+        <v>1.3831</v>
+      </c>
+      <c r="AE35">
+        <v>0.97435700000000003</v>
+      </c>
+      <c r="AF35">
+        <v>1976.14</v>
+      </c>
+      <c r="AG35">
+        <f>1000/AVERAGE(AF31:AF35)</f>
+        <v>0.54371702356252105</v>
+      </c>
+      <c r="AJ35">
+        <v>1000000</v>
+      </c>
+      <c r="AK35">
+        <v>1.38541</v>
+      </c>
+      <c r="AL35">
+        <v>0.87406899999999998</v>
+      </c>
+      <c r="AM35">
+        <v>1771.7</v>
+      </c>
+      <c r="AN35">
+        <f>1000/AVERAGE(AM31:AM35)</f>
+        <v>0.55421865699518158</v>
+      </c>
+    </row>
+    <row r="36" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B36">
+        <v>100000</v>
+      </c>
+      <c r="C36">
+        <v>1199.71</v>
+      </c>
+      <c r="D36">
+        <v>-2930.57</v>
+      </c>
+      <c r="E36">
+        <v>53615.199999999997</v>
+      </c>
+      <c r="F36">
+        <v>31.5609</v>
+      </c>
+      <c r="G36">
+        <v>268</v>
+      </c>
+      <c r="H36">
+        <v>266</v>
+      </c>
+      <c r="I36">
+        <v>266</v>
+      </c>
+      <c r="J36">
+        <v>800</v>
+      </c>
+      <c r="K36">
+        <f>G36*$G$19+H36*$H$19+I36*$I$19+J36*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L36">
+        <f>(K36*1.66E-24)/(E36*1E-24)</f>
+        <v>1.4469897432071506</v>
+      </c>
+      <c r="N36">
+        <v>467.84800000000001</v>
+      </c>
+      <c r="O36">
+        <f>AVERAGE(N36:N39)</f>
+        <v>482.40699999999998</v>
+      </c>
+      <c r="Q36">
+        <f>D36+(1.5*(0.000086173)*C36*SUM(G36:J36))</f>
+        <v>-2682.4517364080002</v>
+      </c>
+      <c r="R36" cm="1">
+        <f t="array" ref="R36:S36">LINEST(Q36:Q39,C36:C39)</f>
+        <v>0.57015572565283368</v>
+      </c>
+      <c r="S36">
+        <v>-3365.9029254708753</v>
+      </c>
+    </row>
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B37">
+        <v>100000</v>
+      </c>
+      <c r="C37">
+        <v>1297.21</v>
+      </c>
+      <c r="D37">
+        <v>-2893.74</v>
+      </c>
+      <c r="E37">
+        <v>55546.6</v>
+      </c>
+      <c r="F37">
+        <v>-47.743099999999998</v>
+      </c>
+      <c r="G37">
+        <v>268</v>
+      </c>
+      <c r="H37">
+        <v>266</v>
+      </c>
+      <c r="I37">
+        <v>266</v>
+      </c>
+      <c r="J37">
+        <v>800</v>
+      </c>
+      <c r="K37">
+        <f t="shared" ref="K37:K39" si="8">G37*$G$19+H37*$H$19+I37*$I$19+J37*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L37">
+        <f t="shared" ref="L37:L39" si="9">(K37*1.66E-24)/(E37*1E-24)</f>
+        <v>1.3966767449312834</v>
+      </c>
+      <c r="N37">
+        <v>477.08699999999999</v>
+      </c>
+      <c r="O37" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" ref="Q37:Q39" si="10">D37+(1.5*(0.000086173)*C37*SUM(G37:J37))</f>
+        <v>-2625.4572544079997</v>
+      </c>
+      <c r="R37">
+        <f>R36/SUM(G36:I36)*(1.602E-19)*(6.022E+23)</f>
+        <v>68.755392542124341</v>
+      </c>
+      <c r="S37" t="s">
+        <v>66</v>
+      </c>
+      <c r="U37">
+        <v>1500</v>
+      </c>
+      <c r="V37">
+        <v>600000</v>
+      </c>
+      <c r="W37">
+        <v>1.3419399999999999</v>
+      </c>
+      <c r="X37">
+        <v>0.93457699999999999</v>
+      </c>
+      <c r="Y37">
+        <v>1914.65</v>
+      </c>
+      <c r="AB37">
+        <v>1500</v>
+      </c>
+      <c r="AC37">
+        <v>600000</v>
+      </c>
+      <c r="AD37">
+        <v>1.34093</v>
+      </c>
+      <c r="AE37">
+        <v>1.03305</v>
+      </c>
+      <c r="AF37">
+        <v>2116.84</v>
+      </c>
+      <c r="AI37">
+        <v>1500</v>
+      </c>
+      <c r="AJ37">
+        <v>600000</v>
+      </c>
+      <c r="AK37">
+        <v>1.3413299999999999</v>
+      </c>
+      <c r="AL37">
+        <v>1.05949</v>
+      </c>
+      <c r="AM37">
+        <v>2170.79</v>
+      </c>
+    </row>
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <v>100000</v>
+      </c>
+      <c r="C38">
+        <v>1400.77</v>
+      </c>
+      <c r="D38">
+        <v>-2856.93</v>
+      </c>
+      <c r="E38">
+        <v>57397.7</v>
+      </c>
+      <c r="F38">
+        <v>13.9192</v>
+      </c>
+      <c r="G38">
+        <v>268</v>
+      </c>
+      <c r="H38">
+        <v>266</v>
+      </c>
+      <c r="I38">
+        <v>266</v>
+      </c>
+      <c r="J38">
+        <v>800</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="8"/>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="9"/>
+        <v>1.351633331649178</v>
+      </c>
+      <c r="N38">
+        <v>487.702</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="10"/>
+        <v>-2567.2294722959996</v>
+      </c>
+      <c r="V38">
+        <v>700000</v>
+      </c>
+      <c r="W38">
+        <v>1.3405899999999999</v>
+      </c>
+      <c r="X38">
+        <v>0.88179399999999997</v>
+      </c>
+      <c r="Y38">
+        <v>1807.08</v>
+      </c>
+      <c r="AC38">
+        <v>700000</v>
+      </c>
+      <c r="AD38">
+        <v>1.3422499999999999</v>
+      </c>
+      <c r="AE38">
+        <v>0.97532300000000005</v>
+      </c>
+      <c r="AF38">
+        <v>1997.95</v>
+      </c>
+      <c r="AJ38">
+        <v>700000</v>
+      </c>
+      <c r="AK38">
+        <v>1.34053</v>
+      </c>
+      <c r="AL38">
+        <v>1.0025599999999999</v>
+      </c>
+      <c r="AM38">
+        <v>2054.5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <v>100000</v>
+      </c>
+      <c r="C39">
+        <v>1501.85</v>
+      </c>
+      <c r="D39">
+        <v>-2820.5</v>
+      </c>
+      <c r="E39">
+        <v>59661.8</v>
+      </c>
+      <c r="F39">
+        <v>55.202199999999998</v>
+      </c>
+      <c r="G39">
+        <v>268</v>
+      </c>
+      <c r="H39">
+        <v>266</v>
+      </c>
+      <c r="I39">
+        <v>266</v>
+      </c>
+      <c r="J39">
+        <v>800</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="8"/>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="9"/>
+        <v>1.3003403263059448</v>
+      </c>
+      <c r="N39">
+        <v>496.99099999999999</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="10"/>
+        <v>-2509.89459188</v>
+      </c>
+      <c r="V39">
+        <v>800000</v>
+      </c>
+      <c r="W39">
+        <v>1.3432500000000001</v>
+      </c>
+      <c r="X39">
+        <v>0.97180900000000003</v>
+      </c>
+      <c r="Y39">
+        <v>1990.1</v>
+      </c>
+      <c r="AC39">
+        <v>800000</v>
+      </c>
+      <c r="AD39">
+        <v>1.3402400000000001</v>
+      </c>
+      <c r="AE39">
+        <v>1.11494</v>
+      </c>
+      <c r="AF39">
+        <v>2285</v>
+      </c>
+      <c r="AJ39">
+        <v>800000</v>
+      </c>
+      <c r="AK39">
+        <v>1.34226</v>
+      </c>
+      <c r="AL39">
+        <v>1.0099400000000001</v>
+      </c>
+      <c r="AM39">
+        <v>2068.79</v>
+      </c>
+    </row>
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="V40">
+        <v>900000</v>
+      </c>
+      <c r="W40">
+        <v>1.3404100000000001</v>
+      </c>
+      <c r="X40">
+        <v>0.99210200000000004</v>
+      </c>
+      <c r="Y40">
+        <v>2033.18</v>
+      </c>
+      <c r="AC40">
+        <v>900000</v>
+      </c>
+      <c r="AD40">
+        <v>1.3409899999999999</v>
+      </c>
+      <c r="AE40">
+        <v>0.99912900000000004</v>
+      </c>
+      <c r="AF40">
+        <v>2047.26</v>
+      </c>
+      <c r="AJ40">
+        <v>900000</v>
+      </c>
+      <c r="AK40">
+        <v>1.3431500000000001</v>
+      </c>
+      <c r="AL40">
+        <v>0.96774099999999996</v>
+      </c>
+      <c r="AM40">
+        <v>1981.97</v>
+      </c>
+    </row>
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>63</v>
+      </c>
+      <c r="V41">
+        <v>1000000</v>
+      </c>
+      <c r="W41">
+        <v>1.34057</v>
+      </c>
+      <c r="X41">
+        <v>1.0477099999999999</v>
+      </c>
+      <c r="Y41">
+        <v>2147.06</v>
+      </c>
+      <c r="Z41">
+        <f>1000/AVERAGE(Y37:Y41)</f>
+        <v>0.50545537991542722</v>
+      </c>
+      <c r="AC41">
+        <v>1000000</v>
+      </c>
+      <c r="AD41">
+        <v>1.3399099999999999</v>
+      </c>
+      <c r="AE41">
+        <v>1.1496599999999999</v>
+      </c>
+      <c r="AF41">
+        <v>2356.4</v>
+      </c>
+      <c r="AG41">
+        <f>1000/AVERAGE(AF37:AF41)</f>
+        <v>0.46281511924431556</v>
+      </c>
+      <c r="AJ41">
+        <v>1000000</v>
+      </c>
+      <c r="AK41">
+        <v>1.34287</v>
+      </c>
+      <c r="AL41">
+        <v>0.863039</v>
+      </c>
+      <c r="AM41">
+        <v>1767.62</v>
+      </c>
+      <c r="AN41">
+        <f>1000/AVERAGE(AM37:AM41)</f>
+        <v>0.49782599388470555</v>
+      </c>
+    </row>
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>100000</v>
+      </c>
+      <c r="C43">
+        <v>1200.46</v>
+      </c>
+      <c r="D43">
+        <v>-2923.09</v>
+      </c>
+      <c r="E43">
+        <v>54564.800000000003</v>
+      </c>
+      <c r="F43">
+        <v>20.658200000000001</v>
+      </c>
+      <c r="G43">
+        <v>268</v>
+      </c>
+      <c r="H43">
+        <v>266</v>
+      </c>
+      <c r="I43">
+        <v>266</v>
+      </c>
+      <c r="J43">
+        <v>800</v>
+      </c>
+      <c r="K43">
+        <f>G43*$G$19+H43*$H$19+I43*$I$19+J43*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L43">
+        <f>(K43*1.66E-24)/(E43*1E-24)</f>
+        <v>1.4218075477230747</v>
+      </c>
+      <c r="N43">
+        <v>1.4350000000000001</v>
+      </c>
+      <c r="O43">
+        <f>AVERAGE(N43:N46)*1000</f>
+        <v>1477.75</v>
+      </c>
+      <c r="Q43">
+        <f>D43+(1.5*(0.000086173)*C43*SUM(G43:J43))</f>
+        <v>-2674.8166250080003</v>
+      </c>
+      <c r="R43" cm="1">
+        <f t="array" ref="R43:S43">LINEST(Q43:Q46,C43:C46)</f>
+        <v>0.55423655017684026</v>
+      </c>
+      <c r="S43">
+        <v>-3339.8791453260205</v>
+      </c>
+      <c r="V43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B44">
+        <v>100000</v>
+      </c>
+      <c r="C44">
+        <v>1302.1099999999999</v>
+      </c>
+      <c r="D44">
+        <v>-2886.67</v>
+      </c>
+      <c r="E44">
+        <v>56409.9</v>
+      </c>
+      <c r="F44">
+        <v>11.6927</v>
+      </c>
+      <c r="G44">
+        <v>268</v>
+      </c>
+      <c r="H44">
+        <v>266</v>
+      </c>
+      <c r="I44">
+        <v>266</v>
+      </c>
+      <c r="J44">
+        <v>800</v>
+      </c>
+      <c r="K44">
+        <f t="shared" ref="K44:K46" si="11">G44*$G$19+H44*$H$19+I44*$I$19+J44*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L44">
+        <f t="shared" ref="L44:L46" si="12">(K44*1.66E-24)/(E44*1E-24)</f>
+        <v>1.37530193246221</v>
+      </c>
+      <c r="N44">
+        <v>1.4770000000000001</v>
+      </c>
+      <c r="O44" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" ref="Q44:Q46" si="13">D44+(1.5*(0.000086173)*C44*SUM(G44:J44))</f>
+        <v>-2617.373859928</v>
+      </c>
+      <c r="R44">
+        <f>R43/SUM(G43:I43)*(1.602E-19)*(6.022E+23)</f>
+        <v>66.835690415927758</v>
+      </c>
+      <c r="S44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B45">
+        <v>100000</v>
+      </c>
+      <c r="C45">
+        <v>1402.2</v>
+      </c>
+      <c r="D45">
+        <v>-2853.55</v>
+      </c>
+      <c r="E45">
+        <v>58157.5</v>
+      </c>
+      <c r="F45">
+        <v>24.378900000000002</v>
+      </c>
+      <c r="G45">
+        <v>268</v>
+      </c>
+      <c r="H45">
+        <v>266</v>
+      </c>
+      <c r="I45">
+        <v>266</v>
+      </c>
+      <c r="J45">
+        <v>800</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="11"/>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="12"/>
+        <v>1.3339748868159742</v>
+      </c>
+      <c r="N45">
+        <v>1.496</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="13"/>
+        <v>-2563.5537265600001</v>
+      </c>
+      <c r="U45">
+        <v>1200</v>
+      </c>
+      <c r="V45">
+        <v>600000</v>
+      </c>
+      <c r="W45">
+        <v>1.4699800000000001</v>
+      </c>
+      <c r="X45">
+        <v>0.69882599999999995</v>
+      </c>
+      <c r="Y45">
+        <v>1388.8</v>
+      </c>
+      <c r="AB45">
+        <v>1200</v>
+      </c>
+      <c r="AC45">
+        <v>600000</v>
+      </c>
+      <c r="AD45">
+        <v>1.47096</v>
+      </c>
+      <c r="AE45">
+        <v>0.63085599999999997</v>
+      </c>
+      <c r="AF45">
+        <v>1253.3900000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B46">
+        <v>100000</v>
+      </c>
+      <c r="C46">
+        <v>1501.71</v>
+      </c>
+      <c r="D46">
+        <v>-2817.88</v>
+      </c>
+      <c r="E46">
+        <v>60303.3</v>
+      </c>
+      <c r="F46">
+        <v>-105.19499999999999</v>
+      </c>
+      <c r="G46">
+        <v>268</v>
+      </c>
+      <c r="H46">
+        <v>266</v>
+      </c>
+      <c r="I46">
+        <v>266</v>
+      </c>
+      <c r="J46">
+        <v>800</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="11"/>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="12"/>
+        <v>1.2865074461928288</v>
+      </c>
+      <c r="N46">
+        <v>1.5029999999999999</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="13"/>
+        <v>-2507.303546008</v>
+      </c>
+      <c r="V46">
+        <v>700000</v>
+      </c>
+      <c r="W46">
+        <v>1.47014</v>
+      </c>
+      <c r="X46">
+        <v>0.77110999999999996</v>
+      </c>
+      <c r="Y46">
+        <v>1532.36</v>
+      </c>
+      <c r="AC46">
+        <v>700000</v>
+      </c>
+      <c r="AD46">
+        <v>1.4699500000000001</v>
+      </c>
+      <c r="AE46">
+        <v>0.58769199999999999</v>
+      </c>
+      <c r="AF46">
+        <v>1167.92</v>
+      </c>
+    </row>
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="V47">
+        <v>800000</v>
+      </c>
+      <c r="W47">
+        <v>1.47072</v>
+      </c>
+      <c r="X47">
+        <v>0.66481299999999999</v>
+      </c>
+      <c r="Y47">
+        <v>1320.95</v>
+      </c>
+      <c r="AC47">
+        <v>800000</v>
+      </c>
+      <c r="AD47">
+        <v>1.4705999999999999</v>
+      </c>
+      <c r="AE47">
+        <v>0.68200400000000005</v>
+      </c>
+      <c r="AF47">
+        <v>1355.13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>72</v>
+      </c>
+      <c r="V48">
+        <v>900000</v>
+      </c>
+      <c r="W48">
+        <v>1.47227</v>
+      </c>
+      <c r="X48">
+        <v>0.50766599999999995</v>
+      </c>
+      <c r="Y48">
+        <v>1008.35</v>
+      </c>
+      <c r="AC48">
+        <v>900000</v>
+      </c>
+      <c r="AD48">
+        <v>1.4709000000000001</v>
+      </c>
+      <c r="AE48">
+        <v>0.76884799999999998</v>
+      </c>
+      <c r="AF48">
+        <v>1527.59</v>
+      </c>
+    </row>
+    <row r="49" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V49">
+        <v>1000000</v>
+      </c>
+      <c r="W49">
+        <v>1.47113</v>
+      </c>
+      <c r="X49">
+        <v>0.61738599999999999</v>
+      </c>
+      <c r="Y49">
+        <v>1226.6099999999999</v>
+      </c>
+      <c r="Z49">
+        <f>1000/AVERAGE(Y45:Y49)</f>
+        <v>0.77195398536684023</v>
+      </c>
+      <c r="AC49">
+        <v>1000000</v>
+      </c>
+      <c r="AD49">
+        <v>1.4709099999999999</v>
+      </c>
+      <c r="AE49">
+        <v>0.66286699999999998</v>
+      </c>
+      <c r="AF49">
+        <v>1316.99</v>
+      </c>
+      <c r="AG49">
+        <f>1000/AVERAGE(AF45:AF49)</f>
+        <v>0.7551706534642697</v>
+      </c>
+    </row>
+    <row r="50" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="B50">
+        <v>100000</v>
+      </c>
+      <c r="C50">
+        <v>1201.48</v>
+      </c>
+      <c r="D50">
+        <v>-2928.83</v>
+      </c>
+      <c r="E50">
+        <v>53946.7</v>
+      </c>
+      <c r="F50">
+        <v>-21.6539</v>
+      </c>
+      <c r="G50">
+        <v>268</v>
+      </c>
+      <c r="H50">
+        <v>266</v>
+      </c>
+      <c r="I50">
+        <v>266</v>
+      </c>
+      <c r="J50">
+        <v>800</v>
+      </c>
+      <c r="K50">
+        <f>G50*$G$19+H50*$H$19+I50*$I$19+J50*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L50">
+        <f>(K50*1.66E-24)/(E50*1E-24)</f>
+        <v>1.4380980575271523</v>
+      </c>
+      <c r="N50">
+        <v>2.323</v>
+      </c>
+      <c r="O50">
+        <f>AVERAGE(N50:N53)*1000</f>
+        <v>2360.5</v>
+      </c>
+      <c r="Q50">
+        <f>D50+(1.5*(0.000086173)*C50*SUM(G50:J50))</f>
+        <v>-2680.3456735039999</v>
+      </c>
+      <c r="R50" cm="1">
+        <f t="array" ref="R50:S50">LINEST(Q50:Q53,C50:C53)</f>
+        <v>0.55951581292907715</v>
+      </c>
+      <c r="S50">
+        <v>-3352.0078835858026</v>
+      </c>
+    </row>
+    <row r="51" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="B51">
+        <v>100000</v>
+      </c>
+      <c r="C51">
+        <v>1300.06</v>
+      </c>
+      <c r="D51">
+        <v>-2892.71</v>
+      </c>
+      <c r="E51">
+        <v>55663.9</v>
+      </c>
+      <c r="F51">
+        <v>13.9526</v>
+      </c>
+      <c r="G51">
+        <v>268</v>
+      </c>
+      <c r="H51">
+        <v>266</v>
+      </c>
+      <c r="I51">
+        <v>266</v>
+      </c>
+      <c r="J51">
+        <v>800</v>
+      </c>
+      <c r="K51">
+        <f t="shared" ref="K51:K53" si="14">G51*$G$19+H51*$H$19+I51*$I$19+J51*$J$19</f>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L51">
+        <f t="shared" ref="L51:L53" si="15">(K51*1.66E-24)/(E51*1E-24)</f>
+        <v>1.3937335414873917</v>
+      </c>
+      <c r="N51">
+        <v>2.3410000000000002</v>
+      </c>
+      <c r="O51" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" ref="Q51:Q53" si="16">D51+(1.5*(0.000086173)*C51*SUM(G51:J51))</f>
+        <v>-2623.8378310879998</v>
+      </c>
+      <c r="R51">
+        <f>R50/SUM(G50:I50)*(1.602E-19)*(6.022E+23)</f>
+        <v>67.472319614814538</v>
+      </c>
+      <c r="S51" t="s">
+        <v>66</v>
+      </c>
+      <c r="U51">
+        <v>1300</v>
+      </c>
+      <c r="V51">
+        <v>600000</v>
+      </c>
+      <c r="W51">
+        <v>1.42882</v>
+      </c>
+      <c r="X51">
+        <v>0.75327500000000003</v>
+      </c>
+      <c r="Y51">
+        <v>1511.21</v>
+      </c>
+      <c r="AB51">
+        <v>1300</v>
+      </c>
+      <c r="AC51">
+        <v>600000</v>
+      </c>
+      <c r="AD51">
+        <v>1.4277299999999999</v>
+      </c>
+      <c r="AE51">
+        <v>0.77840900000000002</v>
+      </c>
+      <c r="AF51">
+        <v>1562.03</v>
+      </c>
+    </row>
+    <row r="52" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <v>100000</v>
+      </c>
+      <c r="C52">
+        <v>1400.77</v>
+      </c>
+      <c r="D52">
+        <v>-2857.74</v>
+      </c>
+      <c r="E52">
+        <v>57500.2</v>
+      </c>
+      <c r="F52">
+        <v>-0.53051899999999996</v>
+      </c>
+      <c r="G52">
+        <v>268</v>
+      </c>
+      <c r="H52">
+        <v>266</v>
+      </c>
+      <c r="I52">
+        <v>266</v>
+      </c>
+      <c r="J52">
+        <v>800</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="14"/>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="15"/>
+        <v>1.3492239066994554</v>
+      </c>
+      <c r="N52">
+        <v>2.3849999999999998</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="16"/>
+        <v>-2568.039472296</v>
+      </c>
+      <c r="V52">
+        <v>700000</v>
+      </c>
+      <c r="W52">
+        <v>1.4287300000000001</v>
+      </c>
+      <c r="X52">
+        <v>0.71347499999999997</v>
+      </c>
+      <c r="Y52">
+        <v>1431.4</v>
+      </c>
+      <c r="AC52">
+        <v>700000</v>
+      </c>
+      <c r="AD52">
+        <v>1.43028</v>
+      </c>
+      <c r="AE52">
+        <v>0.70914299999999997</v>
+      </c>
+      <c r="AF52">
+        <v>1422.26</v>
+      </c>
+    </row>
+    <row r="53" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="B53">
+        <v>100000</v>
+      </c>
+      <c r="C53">
+        <v>1500.18</v>
+      </c>
+      <c r="D53">
+        <v>-2823.29</v>
+      </c>
+      <c r="E53">
+        <v>59296.6</v>
+      </c>
+      <c r="F53">
+        <v>9.8131599999999999</v>
+      </c>
+      <c r="G53">
+        <v>268</v>
+      </c>
+      <c r="H53">
+        <v>266</v>
+      </c>
+      <c r="I53">
+        <v>266</v>
+      </c>
+      <c r="J53">
+        <v>800</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="14"/>
+        <v>46735.328000000001</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="15"/>
+        <v>1.3083489522164848</v>
+      </c>
+      <c r="N53">
+        <v>2.3929999999999998</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="16"/>
+        <v>-2513.0299732640001</v>
+      </c>
+      <c r="V53">
+        <v>800000</v>
+      </c>
+      <c r="W53">
+        <v>1.42848</v>
+      </c>
+      <c r="X53">
+        <v>0.92097099999999998</v>
+      </c>
+      <c r="Y53">
+        <v>1847.83</v>
+      </c>
+      <c r="AC53">
+        <v>800000</v>
+      </c>
+      <c r="AD53">
+        <v>1.42754</v>
+      </c>
+      <c r="AE53">
+        <v>0.78861199999999998</v>
+      </c>
+      <c r="AF53">
+        <v>1582.59</v>
+      </c>
+    </row>
+    <row r="54" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V54">
+        <v>900000</v>
+      </c>
+      <c r="W54">
+        <v>1.4273499999999999</v>
+      </c>
+      <c r="X54">
+        <v>0.82795200000000002</v>
+      </c>
+      <c r="Y54">
+        <v>1661.64</v>
+      </c>
+      <c r="AC54">
+        <v>900000</v>
+      </c>
+      <c r="AD54">
+        <v>1.42726</v>
+      </c>
+      <c r="AE54">
+        <v>0.67081100000000005</v>
+      </c>
+      <c r="AF54">
+        <v>1346.24</v>
+      </c>
+    </row>
+    <row r="55" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V55">
+        <v>1000000</v>
+      </c>
+      <c r="W55">
+        <v>1.4275500000000001</v>
+      </c>
+      <c r="X55">
+        <v>0.72652099999999997</v>
+      </c>
+      <c r="Y55">
+        <v>1457.98</v>
+      </c>
+      <c r="Z55">
+        <f>1000/AVERAGE(Y51:Y55)</f>
+        <v>0.63210645684103528</v>
+      </c>
+      <c r="AC55">
+        <v>1000000</v>
+      </c>
+      <c r="AD55">
+        <v>1.42807</v>
+      </c>
+      <c r="AE55">
+        <v>0.73236000000000001</v>
+      </c>
+      <c r="AF55">
+        <v>1469.51</v>
+      </c>
+      <c r="AG55">
+        <f>1000/AVERAGE(AF51:AF55)</f>
+        <v>0.67726541896316084</v>
+      </c>
+    </row>
+    <row r="57" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="U57">
+        <v>1400</v>
+      </c>
+      <c r="V57">
+        <v>600000</v>
+      </c>
+      <c r="W57">
+        <v>1.38358</v>
+      </c>
+      <c r="X57">
+        <v>0.93840599999999996</v>
+      </c>
+      <c r="Y57">
+        <v>1902.95</v>
+      </c>
+      <c r="AB57">
+        <v>1400</v>
+      </c>
+      <c r="AC57">
+        <v>600000</v>
+      </c>
+      <c r="AD57">
+        <v>1.38473</v>
+      </c>
+      <c r="AE57">
+        <v>0.85072800000000004</v>
+      </c>
+      <c r="AF57">
+        <v>1724.72</v>
+      </c>
+    </row>
+    <row r="58" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V58">
+        <v>700000</v>
+      </c>
+      <c r="W58">
+        <v>1.3832899999999999</v>
+      </c>
+      <c r="X58">
+        <v>0.94225400000000004</v>
+      </c>
+      <c r="Y58">
+        <v>1910.9</v>
+      </c>
+      <c r="AC58">
+        <v>700000</v>
+      </c>
+      <c r="AD58">
+        <v>1.3857200000000001</v>
+      </c>
+      <c r="AE58">
+        <v>0.92573899999999998</v>
+      </c>
+      <c r="AF58">
+        <v>1876.24</v>
+      </c>
+    </row>
+    <row r="59" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V59">
+        <v>800000</v>
+      </c>
+      <c r="W59">
+        <v>1.3843099999999999</v>
+      </c>
+      <c r="X59">
+        <v>0.81150299999999997</v>
+      </c>
+      <c r="Y59">
+        <v>1645.3</v>
+      </c>
+      <c r="AC59">
+        <v>800000</v>
+      </c>
+      <c r="AD59">
+        <v>1.38476</v>
+      </c>
+      <c r="AE59">
+        <v>0.87014899999999995</v>
+      </c>
+      <c r="AF59">
+        <v>1764.04</v>
+      </c>
+    </row>
+    <row r="60" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V60">
+        <v>900000</v>
+      </c>
+      <c r="W60">
+        <v>1.3872100000000001</v>
+      </c>
+      <c r="X60">
+        <v>0.83642799999999995</v>
+      </c>
+      <c r="Y60">
+        <v>1694.67</v>
+      </c>
+      <c r="AC60">
+        <v>900000</v>
+      </c>
+      <c r="AD60">
+        <v>1.3836299999999999</v>
+      </c>
+      <c r="AE60">
+        <v>1.0150699999999999</v>
+      </c>
+      <c r="AF60">
+        <v>2058.31</v>
+      </c>
+    </row>
+    <row r="61" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V61">
+        <v>1000000</v>
+      </c>
+      <c r="W61">
+        <v>1.3845000000000001</v>
+      </c>
+      <c r="X61">
+        <v>1.0313600000000001</v>
+      </c>
+      <c r="Y61">
+        <v>2090.98</v>
+      </c>
+      <c r="Z61">
+        <f>1000/AVERAGE(Y57:Y61)</f>
+        <v>0.54084458290065762</v>
+      </c>
+      <c r="AC61">
+        <v>1000000</v>
+      </c>
+      <c r="AD61">
+        <v>1.3860600000000001</v>
+      </c>
+      <c r="AE61">
+        <v>0.932589</v>
+      </c>
+      <c r="AF61">
+        <v>1889.96</v>
+      </c>
+      <c r="AG61">
+        <f>1000/AVERAGE(AF57:AF61)</f>
+        <v>0.53686836095163137</v>
+      </c>
+    </row>
+    <row r="63" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="U63">
+        <v>1500</v>
+      </c>
+      <c r="V63">
+        <v>600000</v>
+      </c>
+      <c r="W63">
+        <v>1.3413299999999999</v>
+      </c>
+      <c r="X63">
+        <v>0.97601199999999999</v>
+      </c>
+      <c r="Y63">
+        <v>1999.75</v>
+      </c>
+      <c r="AB63">
+        <v>1500</v>
+      </c>
+      <c r="AC63">
+        <v>600000</v>
+      </c>
+      <c r="AD63">
+        <v>1.34097</v>
+      </c>
+      <c r="AE63">
+        <v>0.895204</v>
+      </c>
+      <c r="AF63">
+        <v>1834.28</v>
+      </c>
+    </row>
+    <row r="64" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V64">
+        <v>700000</v>
+      </c>
+      <c r="W64">
+        <v>1.34066</v>
+      </c>
+      <c r="X64">
+        <v>1.0181800000000001</v>
+      </c>
+      <c r="Y64">
+        <v>2086.58</v>
+      </c>
+      <c r="AC64">
+        <v>700000</v>
+      </c>
+      <c r="AD64">
+        <v>1.34155</v>
+      </c>
+      <c r="AE64">
+        <v>1.02149</v>
+      </c>
+      <c r="AF64">
+        <v>2092.87</v>
+      </c>
+    </row>
+    <row r="65" spans="22:33" x14ac:dyDescent="0.2">
+      <c r="V65">
+        <v>800000</v>
+      </c>
+      <c r="W65">
+        <v>1.34154</v>
+      </c>
+      <c r="X65">
+        <v>0.91574</v>
+      </c>
+      <c r="Y65">
+        <v>1876.15</v>
+      </c>
+      <c r="AC65">
+        <v>800000</v>
+      </c>
+      <c r="AD65">
+        <v>1.34016</v>
+      </c>
+      <c r="AE65">
+        <v>0.93160799999999999</v>
+      </c>
+      <c r="AF65">
+        <v>1909.35</v>
+      </c>
+    </row>
+    <row r="66" spans="22:33" x14ac:dyDescent="0.2">
+      <c r="V66">
+        <v>900000</v>
+      </c>
+      <c r="W66">
+        <v>1.3415900000000001</v>
+      </c>
+      <c r="X66">
+        <v>0.98818099999999998</v>
+      </c>
+      <c r="Y66">
+        <v>2024.58</v>
+      </c>
+      <c r="AC66">
+        <v>900000</v>
+      </c>
+      <c r="AD66">
+        <v>1.3408599999999999</v>
+      </c>
+      <c r="AE66">
+        <v>0.89086299999999996</v>
+      </c>
+      <c r="AF66">
+        <v>1825.45</v>
+      </c>
+    </row>
+    <row r="67" spans="22:33" x14ac:dyDescent="0.2">
+      <c r="V67">
+        <v>1000000</v>
+      </c>
+      <c r="W67">
+        <v>1.34124</v>
+      </c>
+      <c r="X67">
+        <v>1.0420100000000001</v>
+      </c>
+      <c r="Y67">
+        <v>2135.11</v>
+      </c>
+      <c r="Z67">
+        <f>1000/AVERAGE(Y63:Y67)</f>
+        <v>0.49396522682389249</v>
+      </c>
+      <c r="AC67">
+        <v>1000000</v>
+      </c>
+      <c r="AD67">
+        <v>1.3403400000000001</v>
+      </c>
+      <c r="AE67">
+        <v>1.0783700000000001</v>
+      </c>
+      <c r="AF67">
+        <v>2210.0500000000002</v>
+      </c>
+      <c r="AG67">
+        <f>1000/AVERAGE(AF63:AF67)</f>
+        <v>0.50648298217179899</v>
       </c>
     </row>
   </sheetData>

--- a/SALT/LiKNaCl_MTP_mk2.xlsx
+++ b/SALT/LiKNaCl_MTP_mk2.xlsx
@@ -1,47 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E5553E-0758-AE4E-8EEC-5EB858AF09F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE9E0D2-5766-F644-B0FC-34867C91959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2120" yWindow="2960" windowWidth="29380" windowHeight="18960" activeTab="1" xr2:uid="{AD1F0662-E479-F942-9113-E180C0D161B9}"/>
+    <workbookView xWindow="2440" yWindow="500" windowWidth="32360" windowHeight="18960" activeTab="1" xr2:uid="{AD1F0662-E479-F942-9113-E180C0D161B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="33.33.33" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'33.33.33'!$U$11:$U$14</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'33.33.33'!$V$11:$V$14</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'33.33.33'!$Y$11:$Y$14</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'33.33.33'!$Z$11:$Z$14</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'33.33.33'!$U$11:$U$14</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'33.33.33'!$V$11:$V$14</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'33.33.33'!$W$11:$W$14</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'33.33.33'!$X$11:$X$14</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'33.33.33'!$Y$11:$Y$14</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'33.33.33'!$Z$11:$Z$14</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'33.33.33'!$U$11:$U$14</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'33.33.33'!$V$11:$V$14</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'33.33.33'!$W$11:$W$14</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'33.33.33'!$W$11:$W$14</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'33.33.33'!$X$11:$X$14</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'33.33.33'!$Y$11:$Y$14</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'33.33.33'!$Z$11:$Z$14</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'33.33.33'!$X$11:$X$14</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'33.33.33'!$Y$11:$Y$14</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'33.33.33'!$Z$11:$Z$14</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'33.33.33'!$U$11:$U$14</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'33.33.33'!$V$11:$V$14</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'33.33.33'!$W$11:$W$14</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'33.33.33'!$X$11:$X$14</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -66,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -88,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
   <si>
     <t>mass</t>
   </si>
@@ -314,13 +288,32 @@
   <si>
     <t>max-min</t>
   </si>
+  <si>
+    <t>kT</t>
+  </si>
+  <si>
+    <t>ln (eta)</t>
+  </si>
+  <si>
+    <t>1/T</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>R^2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -351,12 +344,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3620,7 +3614,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:f>'33.33.33'!$U$5:$U$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3641,7 +3635,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'33.33.33'!$V$11:$V$14</c:f>
+              <c:f>'33.33.33'!$V$5:$V$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3696,7 +3690,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:f>'33.33.33'!$U$5:$U$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3717,7 +3711,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'33.33.33'!$W$11:$W$14</c:f>
+              <c:f>'33.33.33'!$W$5:$W$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3772,7 +3766,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:f>'33.33.33'!$U$5:$U$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3793,7 +3787,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'33.33.33'!$X$11:$X$14</c:f>
+              <c:f>'33.33.33'!$X$5:$X$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3846,9 +3840,59 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.7699037620297464E-3"/>
+                  <c:y val="-0.30887175561388158"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="0.000E+00" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:f>'33.33.33'!$U$5:$U$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3869,7 +3913,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'33.33.33'!$Y$11:$Y$14</c:f>
+              <c:f>'33.33.33'!$Y$5:$Y$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3924,7 +3968,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'33.33.33'!$U$11:$U$14</c:f>
+              <c:f>'33.33.33'!$U$5:$U$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3945,7 +3989,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'33.33.33'!$Z$11:$Z$14</c:f>
+              <c:f>'33.33.33'!$Z$5:$Z$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -6467,15 +6511,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>215900</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6502,16 +6546,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -18272,20 +18316,242 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A437A940-1343-5643-9D4F-169D8F4C58F7}">
-  <dimension ref="B5:AN67"/>
+  <dimension ref="B3:AN67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="22" max="22" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="U3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="V4" t="s">
+        <v>60</v>
+      </c>
+      <c r="W4" t="s">
+        <v>61</v>
+      </c>
+      <c r="X4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>58</v>
       </c>
+      <c r="U5">
+        <v>1200</v>
+      </c>
+      <c r="V5">
+        <v>0.74217781689879514</v>
+      </c>
+      <c r="W5">
+        <v>0.77195398536684023</v>
+      </c>
+      <c r="X5">
+        <v>0.7551706534642697</v>
+      </c>
+      <c r="Y5">
+        <v>0.77498233040286679</v>
+      </c>
+      <c r="Z5">
+        <v>0.82105716035738963</v>
+      </c>
+      <c r="AA5">
+        <f>(0.000086173)*U5</f>
+        <v>0.1034076</v>
+      </c>
+      <c r="AB5">
+        <f>1/U5</f>
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="AC5" cm="1">
+        <f t="array" ref="AC5:AC8">LN(V5:V8)</f>
+        <v>-0.29816641910896663</v>
+      </c>
+      <c r="AD5" cm="1">
+        <f t="array" ref="AD5:AD8">LN(W5:W8)</f>
+        <v>-0.25883033518087467</v>
+      </c>
+      <c r="AE5" cm="1">
+        <f t="array" ref="AE5:AE8">LN(X5:X8)</f>
+        <v>-0.28081152419578498</v>
+      </c>
+      <c r="AF5" cm="1">
+        <f t="array" ref="AF5:AF8">LN(Y5:Y8)</f>
+        <v>-0.25491504936887405</v>
+      </c>
+      <c r="AG5" cm="1">
+        <f t="array" ref="AG5:AG8">LN(Z5:Z8)</f>
+        <v>-0.19716254910626355</v>
+      </c>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="U6">
+        <v>1300</v>
+      </c>
+      <c r="V6">
+        <v>0.68435402454914762</v>
+      </c>
+      <c r="W6">
+        <v>0.63210645684103528</v>
+      </c>
+      <c r="X6">
+        <v>0.67726541896316084</v>
+      </c>
+      <c r="Y6">
+        <v>0.60724491766366162</v>
+      </c>
+      <c r="Z6">
+        <v>0.6562868340985637</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" ref="AA6:AA8" si="0">(0.000086173)*U6</f>
+        <v>0.11202490000000001</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" ref="AB6:AB8" si="1">1/U6</f>
+        <v>7.6923076923076923E-4</v>
+      </c>
+      <c r="AC6">
+        <v>-0.37927991550756968</v>
+      </c>
+      <c r="AD6">
+        <v>-0.45869745465171269</v>
+      </c>
+      <c r="AE6">
+        <v>-0.38969203125777185</v>
+      </c>
+      <c r="AF6">
+        <v>-0.4988230805648311</v>
+      </c>
+      <c r="AG6">
+        <v>-0.42115733850123693</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>59</v>
       </c>
+      <c r="U7">
+        <v>1400</v>
+      </c>
+      <c r="V7">
+        <v>0.54371702356252105</v>
+      </c>
+      <c r="W7">
+        <v>0.54084458290065762</v>
+      </c>
+      <c r="X7">
+        <v>0.53686836095163137</v>
+      </c>
+      <c r="Y7">
+        <v>0.58232571573653724</v>
+      </c>
+      <c r="Z7">
+        <v>0.55421865699518158</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="0"/>
+        <v>0.1206422</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="1"/>
+        <v>7.1428571428571429E-4</v>
+      </c>
+      <c r="AC7">
+        <v>-0.60932634474010605</v>
+      </c>
+      <c r="AD7">
+        <v>-0.61462331885567878</v>
+      </c>
+      <c r="AE7">
+        <v>-0.62200235241715585</v>
+      </c>
+      <c r="AF7">
+        <v>-0.54072533876396356</v>
+      </c>
+      <c r="AG7">
+        <v>-0.5901959823866274</v>
+      </c>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="U8">
+        <v>1500</v>
+      </c>
+      <c r="V8">
+        <v>0.46281511924431556</v>
+      </c>
+      <c r="W8">
+        <v>0.49396522682389249</v>
+      </c>
+      <c r="X8">
+        <v>0.50648298217179899</v>
+      </c>
+      <c r="Y8">
+        <v>0.50545537991542722</v>
+      </c>
+      <c r="Z8">
+        <v>0.49782599388470555</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>0.1292595</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="1"/>
+        <v>6.6666666666666664E-4</v>
+      </c>
+      <c r="AC8">
+        <v>-0.77042761512900459</v>
+      </c>
+      <c r="AD8">
+        <v>-0.7052901553165325</v>
+      </c>
+      <c r="AE8">
+        <v>-0.68026455472893166</v>
+      </c>
+      <c r="AF8">
+        <v>-0.68229551362542584</v>
+      </c>
+      <c r="AG8">
+        <v>-0.69750467288540519</v>
+      </c>
+    </row>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
         <v>6</v>
       </c>
@@ -18307,11 +18573,8 @@
       <c r="I9" t="s">
         <v>74</v>
       </c>
-      <c r="U9" t="s">
-        <v>70</v>
-      </c>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:33" x14ac:dyDescent="0.2">
       <c r="P10" t="s">
         <v>67</v>
       </c>
@@ -18324,23 +18587,51 @@
       <c r="S10" t="s">
         <v>68</v>
       </c>
-      <c r="V10" t="s">
-        <v>60</v>
-      </c>
-      <c r="W10" t="s">
-        <v>61</v>
-      </c>
-      <c r="X10" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>72</v>
+      <c r="V10">
+        <f>AC$10*EXP(-AC$11/$AA5)</f>
+        <v>0.77267700510560056</v>
+      </c>
+      <c r="W10">
+        <f t="shared" ref="W10:Z12" si="2">AD$10*EXP(-AD$11/$AA5)</f>
+        <v>0.76168818486283663</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="2"/>
+        <v>0.76513764207433421</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="2"/>
+        <v>0.75283399836994436</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="2"/>
+        <v>0.80915756734951871</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC10" s="5">
+        <f>EXP(INTERCEPT(AC5:AC8,$AB5:$AB8))</f>
+        <v>6.7129363359823405E-2</v>
+      </c>
+      <c r="AD10" s="5">
+        <f t="shared" ref="AD10:AG10" si="3">EXP(INTERCEPT(AD5:AD8,$AB5:$AB8))</f>
+        <v>7.9507923600737399E-2</v>
+      </c>
+      <c r="AE10" s="5">
+        <f t="shared" si="3"/>
+        <v>8.9244361226338151E-2</v>
+      </c>
+      <c r="AF10" s="5">
+        <f t="shared" si="3"/>
+        <v>0.1015079411440164</v>
+      </c>
+      <c r="AG10" s="5">
+        <f>EXP(INTERCEPT(AG5:AG8,$AB5:$AB8))</f>
+        <v>6.4929800515558092E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1200</v>
       </c>
@@ -18374,7 +18665,7 @@
         <v>958.14</v>
       </c>
       <c r="Q11" s="4">
-        <f>P11/$P$16</f>
+        <f t="shared" ref="Q11:Q16" si="4">P11/$P$16</f>
         <v>0.35751492537313434</v>
       </c>
       <c r="R11" s="4">
@@ -18384,31 +18675,56 @@
       <c r="S11" s="4">
         <v>66.500148797145641</v>
       </c>
-      <c r="U11">
-        <v>1200</v>
-      </c>
       <c r="V11">
-        <v>0.74217781689879514</v>
+        <f t="shared" ref="V11:V12" si="5">AC$10*EXP(-AC$11/$AA6)</f>
+        <v>0.64028898317011262</v>
       </c>
       <c r="W11">
-        <v>0.77195398536684023</v>
+        <f t="shared" si="2"/>
+        <v>0.64015842357730057</v>
       </c>
       <c r="X11">
-        <v>0.7551706534642697</v>
+        <f t="shared" si="2"/>
+        <v>0.64857189237267188</v>
       </c>
       <c r="Y11">
-        <v>0.77498233040286679</v>
+        <f t="shared" si="2"/>
+        <v>0.64529874944472643</v>
       </c>
       <c r="Z11">
-        <v>0.82105716035738963</v>
+        <f t="shared" si="2"/>
+        <v>0.666433808191359</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC11" s="1">
+        <f>SLOPE(AC5:AC8,$AB5:$AB8)*-1*(0.000086173)</f>
+        <v>-0.25264953924182459</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" ref="AD11:AG11" si="6">SLOPE(AD5:AD8,$AB5:$AB8)*-1*(0.000086173)</f>
+        <v>-0.23366814565759939</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" si="6"/>
+        <v>-0.22218958373805209</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" si="6"/>
+        <v>-0.20719860606587581</v>
+      </c>
+      <c r="AG11" s="1">
+        <f>SLOPE(AG5:AG8,$AB5:$AB8)*-1*(0.000086173)</f>
+        <v>-0.26086500531796997</v>
       </c>
     </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>1300</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:C14" si="0">2.03-0.000505*B12</f>
+        <f t="shared" ref="C12:C14" si="7">2.03-0.000505*B12</f>
         <v>1.3734999999999997</v>
       </c>
       <c r="D12">
@@ -18427,7 +18743,7 @@
         <v>1.3937335414873917</v>
       </c>
       <c r="I12">
-        <f t="shared" ref="I12:I14" si="1">MAX(D12:H12)-MIN(D12:H12)</f>
+        <f t="shared" ref="I12:I14" si="8">MAX(D12:H12)-MIN(D12:H12)</f>
         <v>3.1906084820294334E-2</v>
       </c>
       <c r="O12" t="s">
@@ -18437,41 +18753,66 @@
         <v>681.91300000000001</v>
       </c>
       <c r="Q12" s="4">
-        <f>P12/$P$16</f>
+        <f t="shared" si="4"/>
         <v>0.25444514925373135</v>
       </c>
       <c r="R12" s="4">
-        <f t="shared" ref="R12:R16" si="2">1/Q12</f>
+        <f t="shared" ref="R12:R16" si="9">1/Q12</f>
         <v>3.9301201179622618</v>
       </c>
       <c r="S12" s="4">
         <v>67.79126301354583</v>
       </c>
-      <c r="U12">
-        <v>1300</v>
-      </c>
       <c r="V12">
-        <v>0.68435402454914762</v>
+        <f t="shared" si="5"/>
+        <v>0.54502239868796853</v>
       </c>
       <c r="W12">
-        <v>0.63210645684103528</v>
+        <f t="shared" si="2"/>
+        <v>0.55154628130902239</v>
       </c>
       <c r="X12">
-        <v>0.67726541896316084</v>
+        <f t="shared" si="2"/>
+        <v>0.562899898949071</v>
       </c>
       <c r="Y12">
-        <v>0.60724491766366162</v>
+        <f t="shared" si="2"/>
+        <v>0.56543807816970171</v>
       </c>
       <c r="Z12">
-        <v>0.6562868340985637</v>
+        <f t="shared" si="2"/>
+        <v>0.5643134237466173</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC12" s="1">
+        <f>RSQ(AC5:AC8,$AB5:$AB8)</f>
+        <v>0.95251464951265374</v>
+      </c>
+      <c r="AD12" s="1">
+        <f>RSQ(AD5:AD8,$AB5:$AB8)</f>
+        <v>0.99059921535181172</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" ref="AD12:AG12" si="10">RSQ(AE5:AE8,$AB5:$AB8)</f>
+        <v>0.95733267732440119</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" si="10"/>
+        <v>0.94298104714267639</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" si="10"/>
+        <v>0.99210717807763305</v>
       </c>
     </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>1400</v>
       </c>
       <c r="C13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1.3229999999999997</v>
       </c>
       <c r="D13">
@@ -18490,7 +18831,7 @@
         <v>1.3492239066994554</v>
       </c>
       <c r="I13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>3.0651444378442694E-2</v>
       </c>
       <c r="O13" t="s">
@@ -18500,41 +18841,43 @@
         <v>482.40699999999998</v>
       </c>
       <c r="Q13" s="4">
-        <f>P13/$P$16</f>
+        <f t="shared" si="4"/>
         <v>0.18000261194029851</v>
       </c>
       <c r="R13" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>5.555474941284019</v>
       </c>
       <c r="S13" s="4">
         <v>68.755392542124341</v>
       </c>
-      <c r="U13">
-        <v>1400</v>
-      </c>
       <c r="V13">
-        <v>0.54371702356252105</v>
+        <f>AC$10*EXP(-AC$11/$AA8)</f>
+        <v>0.47400278780415861</v>
       </c>
       <c r="W13">
-        <v>0.54084458290065762</v>
+        <f t="shared" ref="W13:Z13" si="11">AD$10*EXP(-AD$11/$AA8)</f>
+        <v>0.48473441814613577</v>
       </c>
       <c r="X13">
-        <v>0.53686836095163137</v>
+        <f t="shared" si="11"/>
+        <v>0.49786066133748175</v>
       </c>
       <c r="Y13">
-        <v>0.58232571573653724</v>
+        <f t="shared" si="11"/>
+        <v>0.5042656469528104</v>
       </c>
       <c r="Z13">
-        <v>0.55421865699518158</v>
+        <f t="shared" si="11"/>
+        <v>0.48855706026528911</v>
       </c>
     </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1500</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1.2724999999999997</v>
       </c>
       <c r="D14">
@@ -18553,7 +18896,7 @@
         <v>1.3083489522164848</v>
       </c>
       <c r="I14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>4.0187292895770721E-2</v>
       </c>
       <c r="O14" t="s">
@@ -18563,36 +18906,18 @@
         <v>1477.75</v>
       </c>
       <c r="Q14" s="4">
-        <f>P14/$P$16</f>
+        <f t="shared" si="4"/>
         <v>0.55139925373134324</v>
       </c>
       <c r="R14" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>1.8135679242091018</v>
       </c>
       <c r="S14" s="4">
         <v>66.835690415927758</v>
       </c>
-      <c r="U14">
-        <v>1500</v>
-      </c>
-      <c r="V14">
-        <v>0.46281511924431556</v>
-      </c>
-      <c r="W14">
-        <v>0.49396522682389249</v>
-      </c>
-      <c r="X14">
-        <v>0.50648298217179899</v>
-      </c>
-      <c r="Y14">
-        <v>0.50545537991542722</v>
-      </c>
-      <c r="Z14">
-        <v>0.49782599388470555</v>
-      </c>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:33" x14ac:dyDescent="0.2">
       <c r="D15">
         <f>(D11-C11)/C11</f>
         <v>1.9802175900622509E-2</v>
@@ -18604,20 +18929,20 @@
         <v>2360.5</v>
       </c>
       <c r="Q15" s="4">
-        <f>P15/$P$16</f>
+        <f t="shared" si="4"/>
         <v>0.88078358208955221</v>
       </c>
       <c r="R15" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>1.1353526795170514</v>
       </c>
       <c r="S15" s="4">
         <v>67.472319614814538</v>
       </c>
     </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:33" x14ac:dyDescent="0.2">
       <c r="D16">
-        <f t="shared" ref="D16:D18" si="3">(D12-C12)/C12</f>
+        <f t="shared" ref="D16:D17" si="12">(D12-C12)/C12</f>
         <v>2.4541694417549775E-2</v>
       </c>
       <c r="O16" t="s">
@@ -18628,17 +18953,17 @@
         <v>2680</v>
       </c>
       <c r="Q16" s="4">
-        <f>P16/$P$16</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="R16" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:40" x14ac:dyDescent="0.2">
       <c r="D17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>3.1463591227828554E-2</v>
       </c>
       <c r="V17" t="s">
@@ -18946,7 +19271,7 @@
         <v>46735.328000000001</v>
       </c>
       <c r="L23">
-        <f t="shared" ref="L23:L25" si="4">(K23*1.66E-24)/(E23*1E-24)</f>
+        <f t="shared" ref="L23:L25" si="13">(K23*1.66E-24)/(E23*1E-24)</f>
         <v>1.4072080172825043</v>
       </c>
       <c r="N23">
@@ -18956,7 +19281,7 @@
         <v>65</v>
       </c>
       <c r="Q23">
-        <f t="shared" ref="Q23:Q25" si="5">D23+(1.5*(0.000086173)*C23*SUM(G23:J23))</f>
+        <f t="shared" ref="Q23:Q25" si="14">D23+(1.5*(0.000086173)*C23*SUM(G23:J23))</f>
         <v>-2629.3414614880003</v>
       </c>
       <c r="R23">
@@ -19048,14 +19373,14 @@
         <v>46735.328000000001</v>
       </c>
       <c r="L24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>1.3646263311944169</v>
       </c>
       <c r="N24">
         <v>968.99900000000002</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>-2572.8550188240001</v>
       </c>
     </row>
@@ -19092,14 +19417,14 @@
         <v>46735.328000000001</v>
       </c>
       <c r="L25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>1.3253968124454378</v>
       </c>
       <c r="N25">
         <v>977.43</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>-2518.9717242480001</v>
       </c>
       <c r="U25">
@@ -19401,7 +19726,7 @@
         <v>46735.328000000001</v>
       </c>
       <c r="L30">
-        <f t="shared" ref="L30:L32" si="6">(K30*1.66E-24)/(E30*1E-24)</f>
+        <f t="shared" ref="L30:L32" si="15">(K30*1.66E-24)/(E30*1E-24)</f>
         <v>1.3815717960818399</v>
       </c>
       <c r="N30">
@@ -19411,7 +19736,7 @@
         <v>65</v>
       </c>
       <c r="Q30">
-        <f t="shared" ref="Q30:Q32" si="7">D30+(1.5*(0.000086173)*C30*SUM(G30:J30))</f>
+        <f t="shared" ref="Q30:Q32" si="16">D30+(1.5*(0.000086173)*C30*SUM(G30:J30))</f>
         <v>-2620.5122845599999</v>
       </c>
       <c r="R30">
@@ -19455,14 +19780,14 @@
         <v>46735.328000000001</v>
       </c>
       <c r="L31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>1.3349550283232501</v>
       </c>
       <c r="N31">
         <v>682.05100000000004</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>-2564.699988672</v>
       </c>
       <c r="U31">
@@ -19544,14 +19869,14 @@
         <v>46735.328000000001</v>
       </c>
       <c r="L32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>1.2852095195496671</v>
       </c>
       <c r="N32">
         <v>700.79399999999998</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>-2505.9469064240002</v>
       </c>
       <c r="V32">
@@ -19804,11 +20129,11 @@
         <v>800</v>
       </c>
       <c r="K37">
-        <f t="shared" ref="K37:K39" si="8">G37*$G$19+H37*$H$19+I37*$I$19+J37*$J$19</f>
+        <f t="shared" ref="K37:K39" si="17">G37*$G$19+H37*$H$19+I37*$I$19+J37*$J$19</f>
         <v>46735.328000000001</v>
       </c>
       <c r="L37">
-        <f t="shared" ref="L37:L39" si="9">(K37*1.66E-24)/(E37*1E-24)</f>
+        <f t="shared" ref="L37:L39" si="18">(K37*1.66E-24)/(E37*1E-24)</f>
         <v>1.3966767449312834</v>
       </c>
       <c r="N37">
@@ -19818,7 +20143,7 @@
         <v>65</v>
       </c>
       <c r="Q37">
-        <f t="shared" ref="Q37:Q39" si="10">D37+(1.5*(0.000086173)*C37*SUM(G37:J37))</f>
+        <f t="shared" ref="Q37:Q39" si="19">D37+(1.5*(0.000086173)*C37*SUM(G37:J37))</f>
         <v>-2625.4572544079997</v>
       </c>
       <c r="R37">
@@ -19903,18 +20228,18 @@
         <v>800</v>
       </c>
       <c r="K38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>46735.328000000001</v>
       </c>
       <c r="L38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>1.351633331649178</v>
       </c>
       <c r="N38">
         <v>487.702</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>-2567.2294722959996</v>
       </c>
       <c r="V38">
@@ -19983,18 +20308,18 @@
         <v>800</v>
       </c>
       <c r="K39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>46735.328000000001</v>
       </c>
       <c r="L39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>1.3003403263059448</v>
       </c>
       <c r="N39">
         <v>496.99099999999999</v>
       </c>
       <c r="Q39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>-2509.89459188</v>
       </c>
       <c r="V39">
@@ -20215,11 +20540,11 @@
         <v>800</v>
       </c>
       <c r="K44">
-        <f t="shared" ref="K44:K46" si="11">G44*$G$19+H44*$H$19+I44*$I$19+J44*$J$19</f>
+        <f t="shared" ref="K44:K46" si="20">G44*$G$19+H44*$H$19+I44*$I$19+J44*$J$19</f>
         <v>46735.328000000001</v>
       </c>
       <c r="L44">
-        <f t="shared" ref="L44:L46" si="12">(K44*1.66E-24)/(E44*1E-24)</f>
+        <f t="shared" ref="L44:L46" si="21">(K44*1.66E-24)/(E44*1E-24)</f>
         <v>1.37530193246221</v>
       </c>
       <c r="N44">
@@ -20229,7 +20554,7 @@
         <v>65</v>
       </c>
       <c r="Q44">
-        <f t="shared" ref="Q44:Q46" si="13">D44+(1.5*(0.000086173)*C44*SUM(G44:J44))</f>
+        <f t="shared" ref="Q44:Q46" si="22">D44+(1.5*(0.000086173)*C44*SUM(G44:J44))</f>
         <v>-2617.373859928</v>
       </c>
       <c r="R44">
@@ -20269,18 +20594,18 @@
         <v>800</v>
       </c>
       <c r="K45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>46735.328000000001</v>
       </c>
       <c r="L45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>1.3339748868159742</v>
       </c>
       <c r="N45">
         <v>1.496</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>-2563.5537265600001</v>
       </c>
       <c r="U45">
@@ -20343,18 +20668,18 @@
         <v>800</v>
       </c>
       <c r="K46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>46735.328000000001</v>
       </c>
       <c r="L46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>1.2865074461928288</v>
       </c>
       <c r="N46">
         <v>1.5029999999999999</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>-2507.303546008</v>
       </c>
       <c r="V46">
@@ -20555,11 +20880,11 @@
         <v>800</v>
       </c>
       <c r="K51">
-        <f t="shared" ref="K51:K53" si="14">G51*$G$19+H51*$H$19+I51*$I$19+J51*$J$19</f>
+        <f t="shared" ref="K51:K53" si="23">G51*$G$19+H51*$H$19+I51*$I$19+J51*$J$19</f>
         <v>46735.328000000001</v>
       </c>
       <c r="L51">
-        <f t="shared" ref="L51:L53" si="15">(K51*1.66E-24)/(E51*1E-24)</f>
+        <f t="shared" ref="L51:L53" si="24">(K51*1.66E-24)/(E51*1E-24)</f>
         <v>1.3937335414873917</v>
       </c>
       <c r="N51">
@@ -20569,7 +20894,7 @@
         <v>65</v>
       </c>
       <c r="Q51">
-        <f t="shared" ref="Q51:Q53" si="16">D51+(1.5*(0.000086173)*C51*SUM(G51:J51))</f>
+        <f t="shared" ref="Q51:Q53" si="25">D51+(1.5*(0.000086173)*C51*SUM(G51:J51))</f>
         <v>-2623.8378310879998</v>
       </c>
       <c r="R51">
@@ -20639,18 +20964,18 @@
         <v>800</v>
       </c>
       <c r="K52">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>46735.328000000001</v>
       </c>
       <c r="L52">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>1.3492239066994554</v>
       </c>
       <c r="N52">
         <v>2.3849999999999998</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>-2568.039472296</v>
       </c>
       <c r="V52">
@@ -20707,18 +21032,18 @@
         <v>800</v>
       </c>
       <c r="K53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>46735.328000000001</v>
       </c>
       <c r="L53">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>1.3083489522164848</v>
       </c>
       <c r="N53">
         <v>2.3929999999999998</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>-2513.0299732640001</v>
       </c>
       <c r="V53">
